--- a/2026/ITALIA/Octubre/Octubre ITALIA.xlsx
+++ b/2026/ITALIA/Octubre/Octubre ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED8D0B-E09A-4866-B868-1649ECEDF16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FEED97-8B62-4378-8651-9713EDDC2B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$127</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$174</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$175</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="295">
   <si>
     <t>TOTAL</t>
   </si>
@@ -843,12 +843,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">El en mes de septiembre abono la 6ta cuota de 7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">En Septiembre paga la 2da cuota de 9 cuotas de $130.000 </t>
-  </si>
-  <si>
     <t xml:space="preserve">En Septiembre abona la 6ta cuota de 10 - Consta de 10 Cuotas de $165.000 + expensas en curso </t>
   </si>
   <si>
@@ -956,6 +950,15 @@
   </si>
   <si>
     <t>Bayeto Gabriela Paola - Folios de certificacion de firma - Honorarios de certificacion de firma acta 396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El en mes de octubre abono la 7ta cuota de 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En octubre paga la 3er cuota de 9 cuotas de $130.000 </t>
+  </si>
+  <si>
+    <t>Plan de pago 11C : mal imputacion primeras dos cuotas</t>
   </si>
 </sst>
 </file>
@@ -1819,7 +1822,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2205,204 +2208,6 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="7" fillId="11" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2411,6 +2216,208 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="11" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="22" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2782,7 +2789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -2799,12 +2806,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="258" t="s">
+      <c r="B1" s="262" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="259"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="263"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -2817,12 +2824,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="262" t="s">
+      <c r="B3" s="264" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="262"/>
-      <c r="D3" s="262"/>
-      <c r="E3" s="263"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="265"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
@@ -2861,24 +2868,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
-      <c r="B8" s="264" t="s">
+      <c r="B8" s="266" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="264"/>
+      <c r="C8" s="266"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="48"/>
-      <c r="B9" s="264"/>
-      <c r="C9" s="264"/>
+      <c r="B9" s="266"/>
+      <c r="C9" s="266"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
-      <c r="B10" s="264"/>
-      <c r="C10" s="264"/>
+      <c r="B10" s="266"/>
+      <c r="C10" s="266"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
@@ -2897,34 +2904,34 @@
       <c r="E12" s="48"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="265" t="s">
+      <c r="A13" s="267" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="265"/>
-      <c r="C13" s="265"/>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
+      <c r="B13" s="267"/>
+      <c r="C13" s="267"/>
+      <c r="D13" s="267"/>
+      <c r="E13" s="267"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="265"/>
-      <c r="B14" s="265"/>
-      <c r="C14" s="265"/>
-      <c r="D14" s="265"/>
-      <c r="E14" s="265"/>
+      <c r="A14" s="267"/>
+      <c r="B14" s="267"/>
+      <c r="C14" s="267"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="265"/>
-      <c r="B15" s="265"/>
-      <c r="C15" s="265"/>
-      <c r="D15" s="265"/>
-      <c r="E15" s="265"/>
+      <c r="A15" s="267"/>
+      <c r="B15" s="267"/>
+      <c r="C15" s="267"/>
+      <c r="D15" s="267"/>
+      <c r="E15" s="267"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="265"/>
-      <c r="B16" s="265"/>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
-      <c r="E16" s="265"/>
+      <c r="A16" s="267"/>
+      <c r="B16" s="267"/>
+      <c r="C16" s="267"/>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
@@ -2966,10 +2973,10 @@
       <c r="E21" s="145"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="260" t="s">
+      <c r="A22" s="253" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="261"/>
+      <c r="B22" s="254"/>
       <c r="C22" s="168"/>
       <c r="D22" s="169">
         <v>2427661.11</v>
@@ -2978,10 +2985,10 @@
       <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="260" t="s">
+      <c r="A23" s="253" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="261"/>
+      <c r="B23" s="254"/>
       <c r="C23" s="168"/>
       <c r="D23" s="169">
         <v>-528016.11</v>
@@ -2990,10 +2997,10 @@
       <c r="H23" s="19"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="260" t="s">
+      <c r="A24" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="261"/>
+      <c r="B24" s="254"/>
       <c r="C24" s="168"/>
       <c r="D24" s="170">
         <v>0</v>
@@ -3004,7 +3011,7 @@
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
@@ -3017,10 +3024,10 @@
       <c r="H25" s="19"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="260" t="s">
+      <c r="A26" s="253" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="261"/>
+      <c r="B26" s="254"/>
       <c r="C26" s="168"/>
       <c r="D26" s="170">
         <v>1136835.6499999999</v>
@@ -3030,10 +3037,10 @@
       <c r="H26" s="19"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="260" t="s">
+      <c r="A27" s="253" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="261"/>
+      <c r="B27" s="254"/>
       <c r="C27" s="168"/>
       <c r="D27" s="170">
         <v>-281366.65000000002</v>
@@ -3043,10 +3050,10 @@
       <c r="H27" s="19"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="260" t="s">
+      <c r="A28" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="261"/>
+      <c r="B28" s="254"/>
       <c r="C28" s="168"/>
       <c r="D28" s="170">
         <v>0</v>
@@ -3165,13 +3172,13 @@
         <v>11886</v>
       </c>
       <c r="E39" s="149" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G39" s="66"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="168" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B40" s="173"/>
       <c r="C40" s="173"/>
@@ -3185,7 +3192,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="168" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B41" s="173"/>
       <c r="C41" s="173"/>
@@ -3306,10 +3313,10 @@
       <c r="E50" s="150"/>
     </row>
     <row r="51" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="253" t="s">
+      <c r="A51" s="257" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="254"/>
+      <c r="B51" s="258"/>
       <c r="C51" s="26"/>
       <c r="D51" s="219">
         <v>7805</v>
@@ -3319,10 +3326,10 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="253" t="s">
+      <c r="A52" s="257" t="s">
         <v>249</v>
       </c>
-      <c r="B52" s="254"/>
+      <c r="B52" s="258"/>
       <c r="C52" s="26"/>
       <c r="D52" s="219">
         <v>7129</v>
@@ -3332,10 +3339,10 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="253" t="s">
+      <c r="A53" s="257" t="s">
         <v>184</v>
       </c>
-      <c r="B53" s="254"/>
+      <c r="B53" s="258"/>
       <c r="C53" s="26"/>
       <c r="D53" s="219">
         <v>213891</v>
@@ -3373,10 +3380,10 @@
         <v>167</v>
       </c>
       <c r="C56" s="29"/>
-      <c r="D56" s="316">
+      <c r="D56" s="250">
         <v>652721.9</v>
       </c>
-      <c r="E56" s="318">
+      <c r="E56" s="252">
         <v>46302</v>
       </c>
     </row>
@@ -3388,11 +3395,11 @@
         <v>169</v>
       </c>
       <c r="C57" s="29"/>
-      <c r="D57" s="316">
+      <c r="D57" s="250">
         <v>17582.669999999998</v>
       </c>
       <c r="E57" s="113" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3421,11 +3428,11 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="255" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B60" s="256"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="316">
+      <c r="D60" s="250">
         <v>4488639.75</v>
       </c>
       <c r="E60" s="113" t="s">
@@ -3433,12 +3440,12 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="253" t="s">
+      <c r="A61" s="257" t="s">
         <v>254</v>
       </c>
-      <c r="B61" s="254"/>
+      <c r="B61" s="258"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="316">
+      <c r="D61" s="250">
         <v>5703910.75</v>
       </c>
       <c r="E61" s="113" t="s">
@@ -3480,11 +3487,11 @@
       </c>
       <c r="B65" s="256"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="316">
+      <c r="D65" s="250">
         <v>285000</v>
       </c>
       <c r="E65" s="159" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3529,11 +3536,11 @@
     </row>
     <row r="69" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="255" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B69" s="256"/>
       <c r="C69" s="29"/>
-      <c r="D69" s="316">
+      <c r="D69" s="250">
         <v>2000000</v>
       </c>
       <c r="E69" s="34" t="s">
@@ -3571,7 +3578,7 @@
     </row>
     <row r="72" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="255" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B72" s="256"/>
       <c r="C72" s="29"/>
@@ -3603,17 +3610,17 @@
       </c>
       <c r="B74" s="17"/>
       <c r="C74" s="29"/>
-      <c r="D74" s="316">
+      <c r="D74" s="250">
         <v>162400</v>
       </c>
       <c r="E74" s="159" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F74" s="50"/>
     </row>
     <row r="75" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="255" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B75" s="256"/>
       <c r="C75" s="29"/>
@@ -3621,7 +3628,7 @@
         <v>215000</v>
       </c>
       <c r="E75" s="159" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F75" s="50"/>
     </row>
@@ -3631,11 +3638,11 @@
       </c>
       <c r="B76" s="17"/>
       <c r="C76" s="29"/>
-      <c r="D76" s="316">
+      <c r="D76" s="250">
         <v>383800</v>
       </c>
       <c r="E76" s="159" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F76" s="50"/>
     </row>
@@ -3645,11 +3652,11 @@
       </c>
       <c r="B77" s="256"/>
       <c r="C77" s="29"/>
-      <c r="D77" s="316">
+      <c r="D77" s="250">
         <v>124611.12</v>
       </c>
       <c r="E77" s="159" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F77" s="50"/>
     </row>
@@ -3692,15 +3699,15 @@
     </row>
     <row r="81" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="255" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B81" s="256"/>
       <c r="C81" s="18"/>
-      <c r="D81" s="317">
+      <c r="D81" s="251">
         <v>200000</v>
       </c>
       <c r="E81" s="159" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3722,11 +3729,11 @@
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="18"/>
-      <c r="D83" s="317">
+      <c r="D83" s="251">
         <v>50000</v>
       </c>
       <c r="E83" s="159" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -3751,10 +3758,10 @@
       <c r="E85" s="41"/>
     </row>
     <row r="86" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="253" t="s">
+      <c r="A86" s="257" t="s">
         <v>255</v>
       </c>
-      <c r="B86" s="254"/>
+      <c r="B86" s="258"/>
       <c r="C86" s="86"/>
       <c r="D86" s="210">
         <f>65000+29590.38</f>
@@ -3763,10 +3770,10 @@
       <c r="E86" s="154"/>
     </row>
     <row r="87" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="253" t="s">
+      <c r="A87" s="257" t="s">
         <v>213</v>
       </c>
-      <c r="B87" s="254"/>
+      <c r="B87" s="258"/>
       <c r="C87" s="86"/>
       <c r="D87" s="210">
         <v>305996.14</v>
@@ -3847,18 +3854,18 @@
       <c r="E95" s="59"/>
     </row>
     <row r="96" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="257"/>
-      <c r="B96" s="257"/>
+      <c r="A96" s="272"/>
+      <c r="B96" s="272"/>
       <c r="C96" s="31"/>
-      <c r="D96" s="249"/>
-      <c r="E96" s="251"/>
+      <c r="D96" s="268"/>
+      <c r="E96" s="270"/>
     </row>
     <row r="97" spans="1:5" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="257"/>
-      <c r="B97" s="257"/>
+      <c r="A97" s="272"/>
+      <c r="B97" s="272"/>
       <c r="C97" s="31"/>
-      <c r="D97" s="250"/>
-      <c r="E97" s="252"/>
+      <c r="D97" s="269"/>
+      <c r="E97" s="271"/>
     </row>
     <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="29"/>
@@ -3977,22 +3984,22 @@
       <c r="E112" s="48"/>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="267" t="s">
+      <c r="A113" s="260" t="s">
         <v>171</v>
       </c>
-      <c r="B113" s="267"/>
+      <c r="B113" s="260"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="267"/>
-      <c r="B114" s="267"/>
+      <c r="A114" s="260"/>
+      <c r="B114" s="260"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="267"/>
-      <c r="B115" s="267"/>
+      <c r="A115" s="260"/>
+      <c r="B115" s="260"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
@@ -4001,22 +4008,22 @@
       <c r="E116" s="48"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="267" t="s">
+      <c r="A117" s="260" t="s">
         <v>219</v>
       </c>
-      <c r="B117" s="267"/>
+      <c r="B117" s="260"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="267"/>
-      <c r="B118" s="267"/>
+      <c r="A118" s="260"/>
+      <c r="B118" s="260"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="267"/>
-      <c r="B119" s="267"/>
+      <c r="A119" s="260"/>
+      <c r="B119" s="260"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
@@ -4025,22 +4032,22 @@
       <c r="E120" s="48"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="267" t="s">
+      <c r="A121" s="260" t="s">
         <v>220</v>
       </c>
-      <c r="B121" s="267"/>
+      <c r="B121" s="260"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="267"/>
-      <c r="B122" s="267"/>
+      <c r="A122" s="260"/>
+      <c r="B122" s="260"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="267"/>
-      <c r="B123" s="267"/>
+      <c r="A123" s="260"/>
+      <c r="B123" s="260"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
@@ -4049,22 +4056,22 @@
       <c r="E124" s="48"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="267" t="s">
+      <c r="A125" s="260" t="s">
         <v>197</v>
       </c>
-      <c r="B125" s="267"/>
+      <c r="B125" s="260"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="267"/>
-      <c r="B126" s="267"/>
+      <c r="A126" s="260"/>
+      <c r="B126" s="260"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
     <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="267"/>
-      <c r="B127" s="267"/>
+      <c r="A127" s="260"/>
+      <c r="B127" s="260"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
@@ -4074,22 +4081,22 @@
       <c r="F128" s="193"/>
     </row>
     <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="267" t="s">
+      <c r="A129" s="260" t="s">
         <v>178</v>
       </c>
-      <c r="B129" s="267"/>
+      <c r="B129" s="260"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
     <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="267"/>
-      <c r="B130" s="267"/>
+      <c r="A130" s="260"/>
+      <c r="B130" s="260"/>
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
     <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="267"/>
-      <c r="B131" s="267"/>
+      <c r="A131" s="260"/>
+      <c r="B131" s="260"/>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
     </row>
@@ -4098,22 +4105,22 @@
       <c r="E132" s="48"/>
     </row>
     <row r="133" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="267" t="s">
+      <c r="A133" s="260" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="267"/>
+      <c r="B133" s="260"/>
       <c r="D133" s="48"/>
       <c r="E133" s="48"/>
     </row>
     <row r="134" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="267"/>
-      <c r="B134" s="267"/>
+      <c r="A134" s="260"/>
+      <c r="B134" s="260"/>
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
     </row>
     <row r="135" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="267"/>
-      <c r="B135" s="267"/>
+      <c r="A135" s="260"/>
+      <c r="B135" s="260"/>
       <c r="D135" s="48"/>
       <c r="E135" s="48"/>
     </row>
@@ -4122,22 +4129,22 @@
       <c r="E136" s="48"/>
     </row>
     <row r="137" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="267" t="s">
+      <c r="A137" s="260" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="267"/>
+      <c r="B137" s="260"/>
       <c r="D137" s="48"/>
       <c r="E137" s="48"/>
     </row>
     <row r="138" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="267"/>
-      <c r="B138" s="267"/>
+      <c r="A138" s="260"/>
+      <c r="B138" s="260"/>
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="267"/>
-      <c r="B139" s="267"/>
+      <c r="A139" s="260"/>
+      <c r="B139" s="260"/>
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
     </row>
@@ -4179,7 +4186,7 @@
         <v>123</v>
       </c>
       <c r="B144" s="206">
-        <f>B174</f>
+        <f>B175</f>
         <v>0</v>
       </c>
       <c r="D144" s="48"/>
@@ -4192,7 +4199,7 @@
       </c>
       <c r="B145" s="207">
         <f>PRORRATEO!F119</f>
-        <v>20030676.670000002</v>
+        <v>24414829.380000003</v>
       </c>
       <c r="D145" s="48"/>
       <c r="E145" s="48"/>
@@ -4200,21 +4207,21 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="204" t="s">
-        <v>286</v>
-      </c>
-      <c r="B146" s="315">
+        <v>284</v>
+      </c>
+      <c r="B146" s="249">
         <v>-161000</v>
       </c>
       <c r="D146" s="48"/>
       <c r="E146" s="48"/>
       <c r="F146" s="66"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="204" t="s">
-        <v>240</v>
-      </c>
-      <c r="B147" s="222">
-        <v>-24000</v>
+        <v>294</v>
+      </c>
+      <c r="B147" s="249">
+        <v>-255000</v>
       </c>
       <c r="D147" s="48"/>
       <c r="E147" s="48"/>
@@ -4222,172 +4229,177 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="204" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B148" s="222">
-        <v>-200000</v>
+        <v>-24000</v>
       </c>
       <c r="D148" s="48"/>
       <c r="E148" s="48"/>
       <c r="F148" s="66"/>
     </row>
-    <row r="149" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="204" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="B149" s="222">
-        <v>-5877</v>
+        <v>-200000</v>
       </c>
       <c r="D149" s="48"/>
       <c r="E149" s="48"/>
       <c r="F149" s="66"/>
     </row>
     <row r="150" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="200" t="s">
+      <c r="A150" s="204" t="s">
+        <v>216</v>
+      </c>
+      <c r="B150" s="222">
+        <v>-5877</v>
+      </c>
+      <c r="D150" s="48"/>
+      <c r="E150" s="48"/>
+      <c r="F150" s="66"/>
+    </row>
+    <row r="151" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="200" t="s">
         <v>159</v>
       </c>
-      <c r="B150" s="201">
-        <f>SUM(B142:C149)</f>
-        <v>-4576206.3600000031</v>
-      </c>
-      <c r="D150" s="211"/>
-      <c r="E150" s="50"/>
-      <c r="F150" s="50"/>
-    </row>
-    <row r="151" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D151" s="48"/>
+      <c r="B151" s="201">
+        <f>SUM(B142:C150)</f>
+        <v>-447053.65000000224</v>
+      </c>
+      <c r="D151" s="211"/>
+      <c r="E151" s="50"/>
+      <c r="F151" s="50"/>
     </row>
     <row r="152" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="268" t="s">
-        <v>266</v>
-      </c>
-      <c r="B152" s="268"/>
-      <c r="C152" s="268"/>
-      <c r="D152" s="268"/>
+      <c r="D152" s="48"/>
     </row>
     <row r="153" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="268"/>
-      <c r="B153" s="268"/>
-      <c r="C153" s="268"/>
-      <c r="D153" s="268"/>
+      <c r="A153" s="261" t="s">
+        <v>264</v>
+      </c>
+      <c r="B153" s="261"/>
+      <c r="C153" s="261"/>
+      <c r="D153" s="261"/>
     </row>
     <row r="154" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="268"/>
-      <c r="B154" s="268"/>
-      <c r="C154" s="268"/>
-      <c r="D154" s="268"/>
+      <c r="A154" s="261"/>
+      <c r="B154" s="261"/>
+      <c r="C154" s="261"/>
+      <c r="D154" s="261"/>
     </row>
     <row r="155" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="268"/>
-      <c r="B155" s="268"/>
-      <c r="C155" s="268"/>
-      <c r="D155" s="268"/>
+      <c r="A155" s="261"/>
+      <c r="B155" s="261"/>
+      <c r="C155" s="261"/>
+      <c r="D155" s="261"/>
     </row>
     <row r="156" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="268"/>
-      <c r="B156" s="268"/>
-      <c r="C156" s="268"/>
-      <c r="D156" s="268"/>
+      <c r="A156" s="261"/>
+      <c r="B156" s="261"/>
+      <c r="C156" s="261"/>
+      <c r="D156" s="261"/>
     </row>
     <row r="157" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="268"/>
-      <c r="B157" s="268"/>
-      <c r="C157" s="268"/>
-      <c r="D157" s="268"/>
+      <c r="A157" s="261"/>
+      <c r="B157" s="261"/>
+      <c r="C157" s="261"/>
+      <c r="D157" s="261"/>
     </row>
     <row r="158" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="268"/>
-      <c r="B158" s="268"/>
-      <c r="C158" s="268"/>
-      <c r="D158" s="268"/>
-    </row>
-    <row r="159" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D159" s="48"/>
-    </row>
-    <row r="160" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="202" t="s">
+      <c r="A158" s="261"/>
+      <c r="B158" s="261"/>
+      <c r="C158" s="261"/>
+      <c r="D158" s="261"/>
+    </row>
+    <row r="159" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="261"/>
+      <c r="B159" s="261"/>
+      <c r="C159" s="261"/>
+      <c r="D159" s="261"/>
+    </row>
+    <row r="160" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D160" s="48"/>
+    </row>
+    <row r="161" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="202" t="s">
+        <v>260</v>
+      </c>
+      <c r="B161" s="203">
+        <v>0</v>
+      </c>
+      <c r="D161" s="48"/>
+    </row>
+    <row r="162" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="204" t="s">
         <v>262</v>
       </c>
-      <c r="B160" s="203">
-        <v>0</v>
-      </c>
-      <c r="D160" s="48"/>
-    </row>
-    <row r="161" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="204" t="s">
-        <v>264</v>
-      </c>
-      <c r="B161" s="207">
+      <c r="B162" s="207">
         <v>320000</v>
       </c>
-      <c r="D161" s="48"/>
-    </row>
-    <row r="162" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="200" t="s">
-        <v>263</v>
-      </c>
-      <c r="B162" s="201">
-        <f>SUM(B160:C161)</f>
+      <c r="D162" s="48"/>
+    </row>
+    <row r="163" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="200" t="s">
+        <v>261</v>
+      </c>
+      <c r="B163" s="201">
+        <f>SUM(B161:C162)</f>
         <v>320000</v>
       </c>
-      <c r="D162" s="48"/>
-    </row>
-    <row r="163" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D163" s="48"/>
     </row>
-    <row r="164" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="202" t="s">
+    <row r="164" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D164" s="48"/>
+    </row>
+    <row r="165" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="202" t="s">
         <v>225</v>
       </c>
-      <c r="B164" s="217">
+      <c r="B165" s="217">
         <v>1506421.54</v>
       </c>
-      <c r="D164" s="48"/>
-    </row>
-    <row r="165" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="208" t="s">
+      <c r="D165" s="48"/>
+    </row>
+    <row r="166" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="208" t="s">
         <v>224</v>
       </c>
-      <c r="B165" s="209">
-        <f>B166-B164</f>
+      <c r="B166" s="209">
+        <f>B167-B165</f>
         <v>23256.959999999963</v>
       </c>
-      <c r="D165" s="48"/>
-    </row>
-    <row r="166" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="200" t="s">
-        <v>274</v>
-      </c>
-      <c r="B166" s="201">
+      <c r="D166" s="48"/>
+    </row>
+    <row r="167" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="200" t="s">
+        <v>272</v>
+      </c>
+      <c r="B167" s="201">
         <v>1529678.5</v>
       </c>
-      <c r="D166" s="48"/>
-    </row>
-    <row r="167" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D167" s="48"/>
     </row>
     <row r="168" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D168" s="48"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A169" s="266" t="s">
+    <row r="169" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D169" s="48"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A170" s="259" t="s">
         <v>124</v>
       </c>
-      <c r="B169" s="266"/>
-      <c r="C169" s="266"/>
-      <c r="D169" s="48"/>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A170" s="266"/>
-      <c r="B170" s="266"/>
-      <c r="C170" s="266"/>
+      <c r="B170" s="259"/>
+      <c r="C170" s="259"/>
       <c r="D170" s="48"/>
     </row>
-    <row r="171" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="69"/>
-      <c r="B171" s="110"/>
-      <c r="C171" s="70"/>
-      <c r="D171" s="212"/>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A171" s="259"/>
+      <c r="B171" s="259"/>
+      <c r="C171" s="259"/>
+      <c r="D171" s="48"/>
     </row>
     <row r="172" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="69"/>
@@ -4399,40 +4411,37 @@
       <c r="A173" s="69"/>
       <c r="B173" s="110"/>
       <c r="C173" s="70"/>
-      <c r="D173" s="56"/>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A174" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B174" s="72">
-        <f>SUM(B171:B173)</f>
-        <v>0</v>
-      </c>
-      <c r="C174" s="73"/>
+      <c r="D173" s="212"/>
+    </row>
+    <row r="174" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="69"/>
+      <c r="B174" s="110"/>
+      <c r="C174" s="70"/>
+      <c r="D174" s="56"/>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M175" s="74"/>
+      <c r="A175" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B175" s="72">
+        <f>SUM(B172:B174)</f>
+        <v>0</v>
+      </c>
+      <c r="C175" s="73"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M176" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A169:C170"/>
-    <mergeCell ref="A125:B127"/>
-    <mergeCell ref="A137:B139"/>
-    <mergeCell ref="A133:B135"/>
-    <mergeCell ref="A113:B115"/>
-    <mergeCell ref="A129:B131"/>
-    <mergeCell ref="A117:B119"/>
-    <mergeCell ref="A121:B123"/>
-    <mergeCell ref="A152:D158"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A96:B97"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A86:B86"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A80:B80"/>
@@ -4449,14 +4458,23 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A96:B97"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A170:C171"/>
+    <mergeCell ref="A125:B127"/>
+    <mergeCell ref="A137:B139"/>
+    <mergeCell ref="A133:B135"/>
+    <mergeCell ref="A113:B115"/>
+    <mergeCell ref="A129:B131"/>
+    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A121:B123"/>
+    <mergeCell ref="A153:D159"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A69:B69"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4492,17 +4510,17 @@
       <c r="A1" s="88"/>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
-      <c r="D1" s="270"/>
-      <c r="E1" s="270"/>
-      <c r="F1" s="270"/>
-      <c r="G1" s="270"/>
-      <c r="H1" s="270"/>
-      <c r="I1" s="270"/>
-      <c r="J1" s="270"/>
-      <c r="K1" s="270"/>
-      <c r="L1" s="270"/>
-      <c r="M1" s="270"/>
-      <c r="N1" s="270"/>
+      <c r="D1" s="288"/>
+      <c r="E1" s="288"/>
+      <c r="F1" s="288"/>
+      <c r="G1" s="288"/>
+      <c r="H1" s="288"/>
+      <c r="I1" s="288"/>
+      <c r="J1" s="288"/>
+      <c r="K1" s="288"/>
+      <c r="L1" s="288"/>
+      <c r="M1" s="288"/>
+      <c r="N1" s="288"/>
       <c r="O1" s="90"/>
     </row>
     <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4512,10 +4530,10 @@
       <c r="D2" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="294">
+      <c r="E2" s="310">
         <v>4500000</v>
       </c>
-      <c r="F2" s="294"/>
+      <c r="F2" s="310"/>
       <c r="G2" s="93"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93" t="s">
@@ -4557,238 +4575,238 @@
       <c r="P3" s="75"/>
     </row>
     <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="271" t="s">
+      <c r="A4" s="289" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="272"/>
-      <c r="C4" s="272"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="272"/>
-      <c r="J4" s="272"/>
-      <c r="K4" s="272"/>
-      <c r="L4" s="272"/>
-      <c r="M4" s="272"/>
-      <c r="N4" s="272"/>
-      <c r="O4" s="273"/>
+      <c r="B4" s="290"/>
+      <c r="C4" s="290"/>
+      <c r="D4" s="290"/>
+      <c r="E4" s="290"/>
+      <c r="F4" s="290"/>
+      <c r="G4" s="290"/>
+      <c r="H4" s="290"/>
+      <c r="I4" s="290"/>
+      <c r="J4" s="290"/>
+      <c r="K4" s="290"/>
+      <c r="L4" s="290"/>
+      <c r="M4" s="290"/>
+      <c r="N4" s="290"/>
+      <c r="O4" s="291"/>
       <c r="P4" s="75"/>
     </row>
     <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="274"/>
-      <c r="B5" s="275"/>
-      <c r="C5" s="275"/>
-      <c r="D5" s="275"/>
-      <c r="E5" s="275"/>
-      <c r="F5" s="275"/>
-      <c r="G5" s="275"/>
-      <c r="H5" s="275"/>
-      <c r="I5" s="275"/>
-      <c r="J5" s="275"/>
-      <c r="K5" s="275"/>
-      <c r="L5" s="275"/>
-      <c r="M5" s="275"/>
-      <c r="N5" s="275"/>
-      <c r="O5" s="276"/>
+      <c r="A5" s="292"/>
+      <c r="B5" s="293"/>
+      <c r="C5" s="293"/>
+      <c r="D5" s="293"/>
+      <c r="E5" s="293"/>
+      <c r="F5" s="293"/>
+      <c r="G5" s="293"/>
+      <c r="H5" s="293"/>
+      <c r="I5" s="293"/>
+      <c r="J5" s="293"/>
+      <c r="K5" s="293"/>
+      <c r="L5" s="293"/>
+      <c r="M5" s="293"/>
+      <c r="N5" s="293"/>
+      <c r="O5" s="294"/>
       <c r="P5" s="75"/>
     </row>
     <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="274"/>
-      <c r="B6" s="275"/>
-      <c r="C6" s="275"/>
-      <c r="D6" s="275"/>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="275"/>
-      <c r="J6" s="275"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="275"/>
-      <c r="N6" s="275"/>
-      <c r="O6" s="276"/>
+      <c r="A6" s="292"/>
+      <c r="B6" s="293"/>
+      <c r="C6" s="293"/>
+      <c r="D6" s="293"/>
+      <c r="E6" s="293"/>
+      <c r="F6" s="293"/>
+      <c r="G6" s="293"/>
+      <c r="H6" s="293"/>
+      <c r="I6" s="293"/>
+      <c r="J6" s="293"/>
+      <c r="K6" s="293"/>
+      <c r="L6" s="293"/>
+      <c r="M6" s="293"/>
+      <c r="N6" s="293"/>
+      <c r="O6" s="294"/>
       <c r="P6" s="75"/>
     </row>
     <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="274"/>
-      <c r="B7" s="275"/>
-      <c r="C7" s="275"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="275"/>
-      <c r="G7" s="275"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="275"/>
-      <c r="O7" s="276"/>
+      <c r="A7" s="292"/>
+      <c r="B7" s="293"/>
+      <c r="C7" s="293"/>
+      <c r="D7" s="293"/>
+      <c r="E7" s="293"/>
+      <c r="F7" s="293"/>
+      <c r="G7" s="293"/>
+      <c r="H7" s="293"/>
+      <c r="I7" s="293"/>
+      <c r="J7" s="293"/>
+      <c r="K7" s="293"/>
+      <c r="L7" s="293"/>
+      <c r="M7" s="293"/>
+      <c r="N7" s="293"/>
+      <c r="O7" s="294"/>
       <c r="P7" s="75"/>
     </row>
     <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="277"/>
-      <c r="B8" s="278"/>
-      <c r="C8" s="278"/>
-      <c r="D8" s="278"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="278"/>
-      <c r="H8" s="278"/>
-      <c r="I8" s="278"/>
-      <c r="J8" s="278"/>
-      <c r="K8" s="278"/>
-      <c r="L8" s="278"/>
-      <c r="M8" s="278"/>
-      <c r="N8" s="278"/>
-      <c r="O8" s="279"/>
+      <c r="A8" s="295"/>
+      <c r="B8" s="296"/>
+      <c r="C8" s="296"/>
+      <c r="D8" s="296"/>
+      <c r="E8" s="296"/>
+      <c r="F8" s="296"/>
+      <c r="G8" s="296"/>
+      <c r="H8" s="296"/>
+      <c r="I8" s="296"/>
+      <c r="J8" s="296"/>
+      <c r="K8" s="296"/>
+      <c r="L8" s="296"/>
+      <c r="M8" s="296"/>
+      <c r="N8" s="296"/>
+      <c r="O8" s="297"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="288" t="s">
+      <c r="A9" s="304" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="289"/>
-      <c r="C9" s="289"/>
-      <c r="D9" s="289"/>
-      <c r="E9" s="289"/>
-      <c r="F9" s="289"/>
-      <c r="G9" s="289"/>
-      <c r="H9" s="289"/>
-      <c r="I9" s="289"/>
-      <c r="J9" s="289"/>
-      <c r="K9" s="289"/>
-      <c r="L9" s="289"/>
-      <c r="M9" s="289"/>
-      <c r="N9" s="289"/>
-      <c r="O9" s="290"/>
+      <c r="B9" s="305"/>
+      <c r="C9" s="305"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="305"/>
+      <c r="K9" s="305"/>
+      <c r="L9" s="305"/>
+      <c r="M9" s="305"/>
+      <c r="N9" s="305"/>
+      <c r="O9" s="306"/>
     </row>
     <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="299" t="s">
+      <c r="A10" s="277" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="300"/>
-      <c r="C10" s="300"/>
-      <c r="D10" s="300"/>
-      <c r="E10" s="300"/>
-      <c r="F10" s="300"/>
-      <c r="G10" s="300"/>
-      <c r="H10" s="300"/>
-      <c r="I10" s="300"/>
-      <c r="J10" s="300"/>
-      <c r="K10" s="300"/>
-      <c r="L10" s="300"/>
-      <c r="M10" s="300"/>
-      <c r="N10" s="300"/>
-      <c r="O10" s="301"/>
+      <c r="B10" s="278"/>
+      <c r="C10" s="278"/>
+      <c r="D10" s="278"/>
+      <c r="E10" s="278"/>
+      <c r="F10" s="278"/>
+      <c r="G10" s="278"/>
+      <c r="H10" s="278"/>
+      <c r="I10" s="278"/>
+      <c r="J10" s="278"/>
+      <c r="K10" s="278"/>
+      <c r="L10" s="278"/>
+      <c r="M10" s="278"/>
+      <c r="N10" s="278"/>
+      <c r="O10" s="279"/>
     </row>
     <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="302" t="s">
+      <c r="A11" s="280" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="303"/>
-      <c r="C11" s="303"/>
-      <c r="D11" s="303"/>
-      <c r="E11" s="303"/>
-      <c r="F11" s="303"/>
-      <c r="G11" s="303"/>
-      <c r="H11" s="303"/>
-      <c r="I11" s="303"/>
-      <c r="J11" s="303"/>
-      <c r="K11" s="303"/>
-      <c r="L11" s="303"/>
-      <c r="M11" s="303"/>
-      <c r="N11" s="303"/>
-      <c r="O11" s="304"/>
+      <c r="B11" s="281"/>
+      <c r="C11" s="281"/>
+      <c r="D11" s="281"/>
+      <c r="E11" s="281"/>
+      <c r="F11" s="281"/>
+      <c r="G11" s="281"/>
+      <c r="H11" s="281"/>
+      <c r="I11" s="281"/>
+      <c r="J11" s="281"/>
+      <c r="K11" s="281"/>
+      <c r="L11" s="281"/>
+      <c r="M11" s="281"/>
+      <c r="N11" s="281"/>
+      <c r="O11" s="282"/>
     </row>
     <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="291" t="s">
+      <c r="A12" s="307" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="292"/>
-      <c r="C12" s="292"/>
-      <c r="D12" s="292"/>
-      <c r="E12" s="292"/>
-      <c r="F12" s="292"/>
-      <c r="G12" s="292"/>
-      <c r="H12" s="292"/>
-      <c r="I12" s="292"/>
-      <c r="J12" s="292"/>
-      <c r="K12" s="292"/>
-      <c r="L12" s="292"/>
-      <c r="M12" s="292"/>
-      <c r="N12" s="292"/>
-      <c r="O12" s="293"/>
+      <c r="B12" s="308"/>
+      <c r="C12" s="308"/>
+      <c r="D12" s="308"/>
+      <c r="E12" s="308"/>
+      <c r="F12" s="308"/>
+      <c r="G12" s="308"/>
+      <c r="H12" s="308"/>
+      <c r="I12" s="308"/>
+      <c r="J12" s="308"/>
+      <c r="K12" s="308"/>
+      <c r="L12" s="308"/>
+      <c r="M12" s="308"/>
+      <c r="N12" s="308"/>
+      <c r="O12" s="309"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="280" t="s">
+      <c r="A13" s="298" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="282" t="s">
+      <c r="B13" s="300" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="282" t="s">
+      <c r="C13" s="300" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="282" t="s">
+      <c r="D13" s="300" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="284" t="s">
+      <c r="E13" s="275" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="282" t="s">
+      <c r="F13" s="300" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="286" t="s">
+      <c r="G13" s="302" t="s">
         <v>133</v>
       </c>
-      <c r="H13" s="284" t="s">
+      <c r="H13" s="275" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="284" t="s">
+      <c r="I13" s="275" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="284" t="s">
+      <c r="J13" s="275" t="s">
         <v>125</v>
       </c>
-      <c r="K13" s="307" t="s">
+      <c r="K13" s="285" t="s">
         <v>217</v>
       </c>
-      <c r="L13" s="295" t="s">
+      <c r="L13" s="311" t="s">
         <v>173</v>
       </c>
-      <c r="M13" s="297" t="s">
+      <c r="M13" s="273" t="s">
         <v>179</v>
       </c>
       <c r="N13" s="138" t="s">
         <v>206</v>
       </c>
-      <c r="O13" s="305" t="s">
+      <c r="O13" s="283" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="281"/>
-      <c r="B14" s="283"/>
-      <c r="C14" s="283"/>
-      <c r="D14" s="283"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="283"/>
-      <c r="G14" s="287"/>
-      <c r="H14" s="285"/>
-      <c r="I14" s="285"/>
-      <c r="J14" s="285"/>
-      <c r="K14" s="308"/>
-      <c r="L14" s="296"/>
-      <c r="M14" s="298"/>
+      <c r="A14" s="299"/>
+      <c r="B14" s="301"/>
+      <c r="C14" s="301"/>
+      <c r="D14" s="301"/>
+      <c r="E14" s="276"/>
+      <c r="F14" s="301"/>
+      <c r="G14" s="303"/>
+      <c r="H14" s="276"/>
+      <c r="I14" s="276"/>
+      <c r="J14" s="276"/>
+      <c r="K14" s="286"/>
+      <c r="L14" s="312"/>
+      <c r="M14" s="274"/>
       <c r="N14" s="139" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O14" s="306"/>
+      <c r="O14" s="284"/>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="124">
@@ -4802,11 +4820,11 @@
         <v>1.37</v>
       </c>
       <c r="E15" s="78">
-        <v>301400.01</v>
-      </c>
-      <c r="F15" s="79">
+        <v>325608.01</v>
+      </c>
+      <c r="F15" s="319">
         <f>E15</f>
-        <v>301400.01</v>
+        <v>325608.01</v>
       </c>
       <c r="G15" s="80">
         <f t="shared" ref="G15:G78" si="0">E15-F15</f>
@@ -4854,16 +4872,16 @@
         <v>1.18</v>
       </c>
       <c r="E16" s="186">
-        <v>4571515.0199999996</v>
+        <v>4989111.0199999996</v>
       </c>
       <c r="F16" s="186"/>
       <c r="G16" s="187">
         <f t="shared" si="0"/>
-        <v>4571515.0199999996</v>
+        <v>4989111.0199999996</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:H79" si="3">IF(G16&gt;0,G16*3%,0)</f>
-        <v>137145.45059999998</v>
+        <v>149673.33059999999</v>
       </c>
       <c r="I16" s="188">
         <f t="shared" ref="I16:I46" si="4">J$2*D16/100</f>
@@ -4881,11 +4899,11 @@
       <c r="M16" s="189"/>
       <c r="N16" s="190">
         <f>ROUND(SUM(G16:M16),0) + P16</f>
-        <v>4989111.0199999996</v>
+        <v>5419235.0199999996</v>
       </c>
       <c r="O16" s="191">
         <f t="shared" si="2"/>
-        <v>5138784.0199999996</v>
+        <v>5581812.0199999996</v>
       </c>
       <c r="P16" s="50">
         <f>P15+0.01</f>
@@ -4907,11 +4925,11 @@
         <v>0.74</v>
       </c>
       <c r="E17" s="78">
-        <v>162800.03</v>
-      </c>
-      <c r="F17" s="79">
-        <f>162000+800.03</f>
-        <v>162800.03</v>
+        <v>181152.03</v>
+      </c>
+      <c r="F17" s="319">
+        <f>E17</f>
+        <v>181152.03</v>
       </c>
       <c r="G17" s="80">
         <f t="shared" si="0"/>
@@ -4960,11 +4978,11 @@
         <v>1.47</v>
       </c>
       <c r="E18" s="79">
-        <v>323400.03999999998</v>
-      </c>
-      <c r="F18" s="79">
+        <v>349375.04</v>
+      </c>
+      <c r="F18" s="319">
         <f>E18</f>
-        <v>323400.03999999998</v>
+        <v>349375.04</v>
       </c>
       <c r="G18" s="106">
         <f t="shared" si="0"/>
@@ -5013,14 +5031,14 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E19" s="79">
-        <v>239520.05</v>
-      </c>
-      <c r="F19" s="79">
-        <v>246706.05</v>
+        <v>259004.05</v>
+      </c>
+      <c r="F19" s="319">
+        <v>259004.05</v>
       </c>
       <c r="G19" s="80">
         <f t="shared" si="0"/>
-        <v>-7186</v>
+        <v>0</v>
       </c>
       <c r="H19" s="80">
         <f t="shared" si="3"/>
@@ -5042,11 +5060,11 @@
       <c r="M19" s="141"/>
       <c r="N19" s="81">
         <f t="shared" si="6"/>
-        <v>259004.05</v>
+        <v>266190.05</v>
       </c>
       <c r="O19" s="134">
         <f t="shared" si="2"/>
-        <v>266774.05</v>
+        <v>274176.05</v>
       </c>
       <c r="P19" s="50">
         <f t="shared" si="7"/>
@@ -5065,14 +5083,14 @@
         <v>1.35</v>
       </c>
       <c r="E20" s="78">
-        <v>296082.06</v>
-      </c>
-      <c r="F20" s="79">
-        <v>307000</v>
+        <v>309937.06</v>
+      </c>
+      <c r="F20" s="319">
+        <v>320000.06</v>
       </c>
       <c r="G20" s="80">
         <f t="shared" si="0"/>
-        <v>-10917.940000000002</v>
+        <v>-10063</v>
       </c>
       <c r="H20" s="80">
         <f t="shared" si="3"/>
@@ -5094,11 +5112,11 @@
       <c r="M20" s="141"/>
       <c r="N20" s="81">
         <f t="shared" si="6"/>
-        <v>309937.06</v>
+        <v>310791.06</v>
       </c>
       <c r="O20" s="134">
         <f t="shared" si="2"/>
-        <v>319235.06</v>
+        <v>320115.06</v>
       </c>
       <c r="P20" s="50">
         <f t="shared" si="7"/>
@@ -5117,11 +5135,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E21" s="78">
-        <v>246400.07</v>
-      </c>
-      <c r="F21" s="79">
+        <v>266190.07</v>
+      </c>
+      <c r="F21" s="319">
         <f>E21</f>
-        <v>246400.07</v>
+        <v>266190.07</v>
       </c>
       <c r="G21" s="80">
         <f t="shared" si="0"/>
@@ -5170,11 +5188,11 @@
         <v>0.82</v>
       </c>
       <c r="E22" s="78">
-        <v>180400.08</v>
-      </c>
-      <c r="F22" s="79">
+        <v>194889.08</v>
+      </c>
+      <c r="F22" s="319">
         <f>E22</f>
-        <v>180400.08</v>
+        <v>194889.08</v>
       </c>
       <c r="G22" s="80">
         <f t="shared" si="0"/>
@@ -5223,14 +5241,15 @@
         <v>0.82</v>
       </c>
       <c r="E23" s="78">
-        <v>175363.09</v>
-      </c>
-      <c r="F23" s="79">
-        <v>180624.09</v>
+        <v>189628.09</v>
+      </c>
+      <c r="F23" s="319">
+        <f>E23</f>
+        <v>189628.09</v>
       </c>
       <c r="G23" s="80">
         <f t="shared" si="0"/>
-        <v>-5261</v>
+        <v>0</v>
       </c>
       <c r="H23" s="80">
         <f t="shared" si="3"/>
@@ -5252,11 +5271,11 @@
       <c r="M23" s="141"/>
       <c r="N23" s="81">
         <f t="shared" si="6"/>
-        <v>189628.09</v>
+        <v>194889.09</v>
       </c>
       <c r="O23" s="134">
         <f t="shared" si="2"/>
-        <v>195317.09</v>
+        <v>200736.09</v>
       </c>
       <c r="P23" s="50">
         <f t="shared" si="7"/>
@@ -5275,11 +5294,11 @@
         <v>1.34</v>
       </c>
       <c r="E24" s="78">
-        <v>294800.09999999998</v>
-      </c>
-      <c r="F24" s="79">
+        <v>318478.09999999998</v>
+      </c>
+      <c r="F24" s="319">
         <f>E24</f>
-        <v>294800.09999999998</v>
+        <v>318478.09999999998</v>
       </c>
       <c r="G24" s="80">
         <f t="shared" si="0"/>
@@ -5328,11 +5347,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E25" s="78">
-        <v>246400.11</v>
-      </c>
-      <c r="F25" s="79">
+        <v>266190.11</v>
+      </c>
+      <c r="F25" s="319">
         <f>E25</f>
-        <v>246400.11</v>
+        <v>266190.11</v>
       </c>
       <c r="G25" s="80">
         <f t="shared" si="0"/>
@@ -5381,18 +5400,18 @@
         <v>1.17</v>
       </c>
       <c r="E26" s="186">
-        <v>5623045.1200000001</v>
-      </c>
-      <c r="F26" s="186">
-        <v>0</v>
+        <v>6069810.1200000001</v>
+      </c>
+      <c r="F26" s="322">
+        <v>1000000.12</v>
       </c>
       <c r="G26" s="187">
         <f t="shared" si="0"/>
-        <v>5623045.1200000001</v>
+        <v>5069810</v>
       </c>
       <c r="H26" s="187">
         <f t="shared" si="3"/>
-        <v>168691.3536</v>
+        <v>152094.29999999999</v>
       </c>
       <c r="I26" s="188">
         <f t="shared" si="4"/>
@@ -5410,11 +5429,11 @@
       <c r="M26" s="189"/>
       <c r="N26" s="190">
         <f t="shared" si="6"/>
-        <v>6069810.1200000001</v>
+        <v>5499978.1200000001</v>
       </c>
       <c r="O26" s="191">
         <f t="shared" si="2"/>
-        <v>6251904.1200000001</v>
+        <v>5664977.1200000001</v>
       </c>
       <c r="P26" s="50">
         <f t="shared" si="7"/>
@@ -5433,11 +5452,11 @@
         <v>1.35</v>
       </c>
       <c r="E27" s="78">
-        <v>297000.13</v>
-      </c>
-      <c r="F27" s="79">
+        <v>320854.13</v>
+      </c>
+      <c r="F27" s="319">
         <f>E27</f>
-        <v>297000.13</v>
+        <v>320854.13</v>
       </c>
       <c r="G27" s="80">
         <f t="shared" si="0"/>
@@ -5486,16 +5505,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E28" s="78">
-        <v>1115946.1399999999</v>
+        <v>1415615.14</v>
       </c>
       <c r="F28" s="79"/>
       <c r="G28" s="80">
         <f t="shared" si="0"/>
-        <v>1115946.1399999999</v>
+        <v>1415615.14</v>
       </c>
       <c r="H28" s="80">
         <f t="shared" si="3"/>
-        <v>33478.384199999993</v>
+        <v>42468.454199999993</v>
       </c>
       <c r="I28" s="120">
         <f t="shared" si="4"/>
@@ -5513,11 +5532,11 @@
       <c r="M28" s="141"/>
       <c r="N28" s="81">
         <f t="shared" si="6"/>
-        <v>1415615.14</v>
+        <v>1724274.14</v>
       </c>
       <c r="O28" s="134">
         <f t="shared" si="2"/>
-        <v>1458083.14</v>
+        <v>1776002.14</v>
       </c>
       <c r="P28" s="50">
         <f t="shared" si="7"/>
@@ -5536,11 +5555,11 @@
         <v>0.82</v>
       </c>
       <c r="E29" s="79">
-        <v>180400.15</v>
-      </c>
-      <c r="F29" s="79">
+        <v>194889.15</v>
+      </c>
+      <c r="F29" s="319">
         <f>E29</f>
-        <v>180400.15</v>
+        <v>194889.15</v>
       </c>
       <c r="G29" s="80">
         <f t="shared" si="0"/>
@@ -5589,11 +5608,11 @@
         <v>0.82</v>
       </c>
       <c r="E30" s="78">
-        <v>180400.16</v>
+        <v>194889.16</v>
       </c>
       <c r="F30" s="79">
         <f>E30</f>
-        <v>180400.16</v>
+        <v>194889.16</v>
       </c>
       <c r="G30" s="80">
         <f t="shared" si="0"/>
@@ -5642,16 +5661,18 @@
         <v>1.34</v>
       </c>
       <c r="E31" s="78">
-        <v>385467.17</v>
-      </c>
-      <c r="F31" s="79"/>
+        <v>715509.17</v>
+      </c>
+      <c r="F31" s="319">
+        <v>193374.17</v>
+      </c>
       <c r="G31" s="80">
         <f t="shared" si="0"/>
-        <v>385467.17</v>
+        <v>522135</v>
       </c>
       <c r="H31" s="80">
         <f t="shared" si="3"/>
-        <v>11564.015099999999</v>
+        <v>15664.05</v>
       </c>
       <c r="I31" s="120">
         <f t="shared" si="4"/>
@@ -5669,11 +5690,11 @@
       <c r="M31" s="141"/>
       <c r="N31" s="81">
         <f t="shared" si="6"/>
-        <v>715509.17</v>
+        <v>856277.17</v>
       </c>
       <c r="O31" s="134">
         <f t="shared" si="2"/>
-        <v>736974.17</v>
+        <v>881965.17</v>
       </c>
       <c r="P31" s="50">
         <f t="shared" si="7"/>
@@ -5692,11 +5713,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E32" s="79">
-        <v>246400.18</v>
-      </c>
-      <c r="F32" s="79">
+        <v>266190.18</v>
+      </c>
+      <c r="F32" s="319">
         <f>E32</f>
-        <v>246400.18</v>
+        <v>266190.18</v>
       </c>
       <c r="G32" s="106">
         <f t="shared" si="0"/>
@@ -5745,11 +5766,10 @@
         <v>1.17</v>
       </c>
       <c r="E33" s="78">
-        <v>223620.19</v>
-      </c>
-      <c r="F33" s="79">
-        <f>E33</f>
-        <v>223620.19</v>
+        <v>278074.19</v>
+      </c>
+      <c r="F33" s="319">
+        <v>278074.19</v>
       </c>
       <c r="G33" s="80">
         <f t="shared" si="0"/>
@@ -5801,14 +5821,14 @@
         <v>1.35</v>
       </c>
       <c r="E34" s="117">
-        <v>1250638.2</v>
+        <v>1328493.2</v>
       </c>
       <c r="F34" s="117">
         <v>366300</v>
       </c>
       <c r="G34" s="118">
         <f t="shared" si="0"/>
-        <v>884338.2</v>
+        <v>962193.2</v>
       </c>
       <c r="H34" s="118"/>
       <c r="I34" s="123">
@@ -5829,18 +5849,18 @@
       </c>
       <c r="N34" s="119">
         <f t="shared" si="6"/>
-        <v>1328493.2</v>
+        <v>1406348.2</v>
       </c>
       <c r="O34" s="136">
         <f t="shared" si="2"/>
-        <v>1368348.2</v>
+        <v>1448538.2</v>
       </c>
       <c r="P34" s="50">
         <f t="shared" ref="P34:P97" si="8">P33+0.01</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="Q34" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -5855,11 +5875,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E35" s="79">
-        <v>246400.21</v>
-      </c>
-      <c r="F35" s="79">
+        <v>266190.21000000002</v>
+      </c>
+      <c r="F35" s="319">
         <f>E35</f>
-        <v>246400.21</v>
+        <v>266190.21000000002</v>
       </c>
       <c r="G35" s="106">
         <f t="shared" si="0"/>
@@ -5909,11 +5929,11 @@
         <v>0.82</v>
       </c>
       <c r="E36" s="78">
-        <v>180400.22</v>
-      </c>
-      <c r="F36" s="79">
+        <v>194889.22</v>
+      </c>
+      <c r="F36" s="319">
         <f>E36</f>
-        <v>180400.22</v>
+        <v>194889.22</v>
       </c>
       <c r="G36" s="80">
         <f t="shared" si="0"/>
@@ -5963,11 +5983,11 @@
         <v>0.82</v>
       </c>
       <c r="E37" s="78">
-        <v>180400.23</v>
-      </c>
-      <c r="F37" s="79">
+        <v>194889.23</v>
+      </c>
+      <c r="F37" s="319">
         <f>E37</f>
-        <v>180400.23</v>
+        <v>194889.23</v>
       </c>
       <c r="G37" s="80">
         <f t="shared" si="0"/>
@@ -6017,19 +6037,18 @@
         <v>1.34</v>
       </c>
       <c r="E38" s="78">
-        <v>294800.24</v>
-      </c>
-      <c r="F38" s="79">
-        <f>E38</f>
-        <v>294800.24</v>
+        <v>328032.24</v>
+      </c>
+      <c r="F38" s="319">
+        <v>318478.24</v>
       </c>
       <c r="G38" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9554</v>
       </c>
       <c r="H38" s="80">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>286.62</v>
       </c>
       <c r="I38" s="120">
         <f t="shared" si="4"/>
@@ -6047,11 +6066,11 @@
       <c r="M38" s="141"/>
       <c r="N38" s="81">
         <f t="shared" si="6"/>
-        <v>318478.24</v>
+        <v>328318.24</v>
       </c>
       <c r="O38" s="134">
         <f t="shared" si="9"/>
-        <v>328032.24</v>
+        <v>338168.24</v>
       </c>
       <c r="P38" s="50">
         <f t="shared" si="8"/>
@@ -6071,16 +6090,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E39" s="78">
-        <v>488450.25</v>
+        <v>769294.25</v>
       </c>
       <c r="F39" s="79"/>
       <c r="G39" s="80">
         <f t="shared" si="0"/>
-        <v>488450.25</v>
+        <v>769294.25</v>
       </c>
       <c r="H39" s="80">
         <f t="shared" si="3"/>
-        <v>14653.5075</v>
+        <v>23078.827499999999</v>
       </c>
       <c r="I39" s="120">
         <f t="shared" si="4"/>
@@ -6098,11 +6117,11 @@
       <c r="M39" s="141"/>
       <c r="N39" s="81">
         <f t="shared" si="6"/>
-        <v>769294.25</v>
+        <v>1058563.25</v>
       </c>
       <c r="O39" s="134">
         <f t="shared" si="9"/>
-        <v>792373.25</v>
+        <v>1090320.25</v>
       </c>
       <c r="P39" s="50">
         <f t="shared" si="8"/>
@@ -6122,11 +6141,11 @@
         <v>1.17</v>
       </c>
       <c r="E40" s="78">
-        <v>265122.65999999997</v>
+        <v>278074.26</v>
       </c>
       <c r="F40" s="79">
         <f>E40</f>
-        <v>265122.65999999997</v>
+        <v>278074.26</v>
       </c>
       <c r="G40" s="80">
         <f t="shared" si="0"/>
@@ -6176,11 +6195,11 @@
         <v>1.35</v>
       </c>
       <c r="E41" s="78">
-        <v>297000.27</v>
-      </c>
-      <c r="F41" s="79">
+        <v>320854.27</v>
+      </c>
+      <c r="F41" s="319">
         <f t="shared" ref="F41" si="11">E41</f>
-        <v>297000.27</v>
+        <v>320854.27</v>
       </c>
       <c r="G41" s="80">
         <f t="shared" si="0"/>
@@ -6230,7 +6249,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E42" s="78">
-        <v>791602.28</v>
+        <v>266190.28000000003</v>
       </c>
       <c r="F42" s="79">
         <f>791603</f>
@@ -6238,7 +6257,7 @@
       </c>
       <c r="G42" s="80">
         <f t="shared" si="0"/>
-        <v>-0.71999999997206032</v>
+        <v>-525412.72</v>
       </c>
       <c r="H42" s="80">
         <f t="shared" si="3"/>
@@ -6260,11 +6279,11 @@
       <c r="M42" s="141"/>
       <c r="N42" s="81">
         <f t="shared" si="6"/>
-        <v>266190.28000000003</v>
+        <v>-259221.72</v>
       </c>
       <c r="O42" s="134">
         <f t="shared" si="9"/>
-        <v>274176.28000000003</v>
+        <v>-266998.71999999997</v>
       </c>
       <c r="P42" s="50">
         <f t="shared" si="8"/>
@@ -6287,11 +6306,11 @@
         <v>0.82</v>
       </c>
       <c r="E43" s="79">
-        <v>180400.29</v>
-      </c>
-      <c r="F43" s="79">
+        <v>194889.29</v>
+      </c>
+      <c r="F43" s="319">
         <f t="shared" ref="F43" si="12">E43</f>
-        <v>180400.29</v>
+        <v>194889.29</v>
       </c>
       <c r="G43" s="106">
         <f t="shared" si="0"/>
@@ -6344,11 +6363,11 @@
         <v>0.82</v>
       </c>
       <c r="E44" s="79">
-        <v>180400.3</v>
-      </c>
-      <c r="F44" s="79">
-        <f>E44</f>
-        <v>180400.3</v>
+        <v>194889.3</v>
+      </c>
+      <c r="F44" s="319">
+        <f>4689+190200.3</f>
+        <v>194889.3</v>
       </c>
       <c r="G44" s="106">
         <f t="shared" si="0"/>
@@ -6398,11 +6417,11 @@
         <v>1.34</v>
       </c>
       <c r="E45" s="78">
-        <v>294800.31</v>
-      </c>
-      <c r="F45" s="79">
+        <v>318478.31</v>
+      </c>
+      <c r="F45" s="319">
         <f>E45</f>
-        <v>294800.31</v>
+        <v>318478.31</v>
       </c>
       <c r="G45" s="80">
         <f t="shared" si="0"/>
@@ -6452,15 +6471,15 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E46" s="78">
-        <v>246400.32</v>
-      </c>
-      <c r="F46" s="79">
-        <f>46400.32+200000.32</f>
-        <v>246400.64000000001</v>
+        <v>266190.32</v>
+      </c>
+      <c r="F46" s="319">
+        <f>2*100000.32+74176</f>
+        <v>274176.64000000001</v>
       </c>
       <c r="G46" s="80">
         <f t="shared" si="0"/>
-        <v>-0.32000000000698492</v>
+        <v>-7986.320000000007</v>
       </c>
       <c r="H46" s="80">
         <f t="shared" si="3"/>
@@ -6482,11 +6501,11 @@
       <c r="M46" s="141"/>
       <c r="N46" s="81">
         <f t="shared" si="6"/>
-        <v>266190.32</v>
+        <v>258204.32</v>
       </c>
       <c r="O46" s="134">
         <f t="shared" si="9"/>
-        <v>274176.32</v>
+        <v>265950.32</v>
       </c>
       <c r="P46" s="50">
         <f t="shared" si="8"/>
@@ -6506,11 +6525,11 @@
         <v>1.17</v>
       </c>
       <c r="E47" s="117">
-        <v>427400.33</v>
-      </c>
-      <c r="F47" s="117">
+        <v>588074.32999999996</v>
+      </c>
+      <c r="F47" s="320">
         <f>E47</f>
-        <v>427400.33</v>
+        <v>588074.32999999996</v>
       </c>
       <c r="G47" s="118">
         <f t="shared" si="0"/>
@@ -6530,25 +6549,25 @@
         <v>120123.879642</v>
       </c>
       <c r="L47" s="123">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="M47" s="143">
-        <v>170000</v>
+        <v>0</v>
       </c>
       <c r="N47" s="119">
         <f t="shared" si="6"/>
-        <v>588074.32999999996</v>
+        <v>278074.33</v>
       </c>
       <c r="O47" s="136">
         <f t="shared" si="9"/>
-        <v>605716.32999999996</v>
+        <v>286416.33</v>
       </c>
       <c r="P47" s="50">
         <f t="shared" si="8"/>
         <v>0.33000000000000013</v>
       </c>
       <c r="Q47" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -6564,11 +6583,11 @@
         <v>1.35</v>
       </c>
       <c r="E48" s="78">
-        <v>297000.34000000003</v>
-      </c>
-      <c r="F48" s="79">
+        <v>320854.34000000003</v>
+      </c>
+      <c r="F48" s="319">
         <f>E48</f>
-        <v>297000.34000000003</v>
+        <v>320854.34000000003</v>
       </c>
       <c r="G48" s="80">
         <f t="shared" si="0"/>
@@ -6618,11 +6637,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E49" s="79">
-        <v>246400.35</v>
-      </c>
-      <c r="F49" s="79">
+        <v>266190.34999999998</v>
+      </c>
+      <c r="F49" s="319">
         <f>E49</f>
-        <v>246400.35</v>
+        <v>266190.34999999998</v>
       </c>
       <c r="G49" s="180">
         <f t="shared" si="0"/>
@@ -6675,11 +6694,11 @@
         <v>0.82</v>
       </c>
       <c r="E50" s="78">
-        <v>180400.36</v>
-      </c>
-      <c r="F50" s="79">
+        <v>194889.36</v>
+      </c>
+      <c r="F50" s="319">
         <f>E50</f>
-        <v>180400.36</v>
+        <v>194889.36</v>
       </c>
       <c r="G50" s="80">
         <f t="shared" si="0"/>
@@ -6732,16 +6751,18 @@
         <v>0.82</v>
       </c>
       <c r="E51" s="79">
-        <v>193106.37</v>
-      </c>
-      <c r="F51" s="79"/>
+        <v>393789.37</v>
+      </c>
+      <c r="F51" s="319">
+        <v>405603.37</v>
+      </c>
       <c r="G51" s="80">
         <f t="shared" si="0"/>
-        <v>193106.37</v>
+        <v>-11814</v>
       </c>
       <c r="H51" s="80">
         <f t="shared" si="3"/>
-        <v>5793.1911</v>
+        <v>0</v>
       </c>
       <c r="I51" s="120">
         <f t="shared" si="13"/>
@@ -6759,11 +6780,11 @@
       <c r="M51" s="141"/>
       <c r="N51" s="81">
         <f t="shared" si="6"/>
-        <v>393789.37</v>
+        <v>183075.37</v>
       </c>
       <c r="O51" s="134">
         <f t="shared" si="9"/>
-        <v>405603.37</v>
+        <v>188567.37</v>
       </c>
       <c r="P51" s="50">
         <f t="shared" si="8"/>
@@ -6786,14 +6807,14 @@
         <v>1.34</v>
       </c>
       <c r="E52" s="117">
-        <v>766200.38</v>
+        <v>789878.38</v>
       </c>
       <c r="F52" s="117">
         <v>484800</v>
       </c>
       <c r="G52" s="118">
         <f t="shared" si="0"/>
-        <v>281400.38</v>
+        <v>305078.38</v>
       </c>
       <c r="H52" s="118">
         <v>0</v>
@@ -6816,18 +6837,18 @@
       </c>
       <c r="N52" s="119">
         <f t="shared" si="6"/>
-        <v>789878.38</v>
+        <v>813556.38</v>
       </c>
       <c r="O52" s="136">
         <f t="shared" si="9"/>
-        <v>813574.38</v>
+        <v>837963.38</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" si="8"/>
         <v>0.38000000000000017</v>
       </c>
       <c r="Q52" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -6843,11 +6864,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E53" s="78">
-        <v>263704.39</v>
+        <v>266190.39</v>
       </c>
       <c r="F53" s="79">
         <f>E53</f>
-        <v>263704.39</v>
+        <v>266190.39</v>
       </c>
       <c r="G53" s="80">
         <f t="shared" si="0"/>
@@ -6897,16 +6918,19 @@
         <v>1.17</v>
       </c>
       <c r="E54" s="78">
-        <v>257400.4</v>
-      </c>
-      <c r="F54" s="79"/>
+        <v>559492.4</v>
+      </c>
+      <c r="F54" s="319">
+        <f>E54</f>
+        <v>559492.4</v>
+      </c>
       <c r="G54" s="80">
         <f t="shared" si="0"/>
-        <v>257400.4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="80">
         <f t="shared" si="3"/>
-        <v>7722.0119999999997</v>
+        <v>0</v>
       </c>
       <c r="I54" s="120">
         <f t="shared" si="13"/>
@@ -6924,11 +6948,11 @@
       <c r="M54" s="141"/>
       <c r="N54" s="81">
         <f t="shared" si="6"/>
-        <v>543196.4</v>
+        <v>278074.40000000002</v>
       </c>
       <c r="O54" s="134">
         <f t="shared" si="9"/>
-        <v>559492.4</v>
+        <v>286416.40000000002</v>
       </c>
       <c r="P54" s="50">
         <f t="shared" si="8"/>
@@ -6948,15 +6972,14 @@
         <v>1.35</v>
       </c>
       <c r="E55" s="78">
-        <v>297000.40999999997</v>
-      </c>
-      <c r="F55" s="79">
-        <f>E55</f>
-        <v>297000.40999999997</v>
+        <v>320854.40999999997</v>
+      </c>
+      <c r="F55" s="319">
+        <v>330481.40999999997</v>
       </c>
       <c r="G55" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-9627</v>
       </c>
       <c r="H55" s="80">
         <f t="shared" si="3"/>
@@ -6978,11 +7001,11 @@
       <c r="M55" s="141"/>
       <c r="N55" s="81">
         <f t="shared" si="6"/>
-        <v>320854.40999999997</v>
+        <v>311227.40999999997</v>
       </c>
       <c r="O55" s="134">
         <f t="shared" si="9"/>
-        <v>330480.40999999997</v>
+        <v>320564.40999999997</v>
       </c>
       <c r="P55" s="50">
         <f t="shared" si="8"/>
@@ -7002,11 +7025,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E56" s="117">
-        <v>279400.42</v>
+        <v>299190.42</v>
       </c>
       <c r="F56" s="117">
         <f>E56</f>
-        <v>279400.42</v>
+        <v>299190.42</v>
       </c>
       <c r="G56" s="118">
         <f t="shared" si="0"/>
@@ -7045,7 +7068,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="Q56" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
@@ -7061,16 +7084,19 @@
         <v>0.82</v>
       </c>
       <c r="E57" s="199">
-        <v>180400.43</v>
-      </c>
-      <c r="F57" s="79"/>
+        <v>380702.43</v>
+      </c>
+      <c r="F57" s="319">
+        <f>186313+194389.43</f>
+        <v>380702.43</v>
+      </c>
       <c r="G57" s="106">
         <f t="shared" si="0"/>
-        <v>180400.43</v>
+        <v>0</v>
       </c>
       <c r="H57" s="106">
         <f t="shared" si="3"/>
-        <v>5412.0128999999997</v>
+        <v>0</v>
       </c>
       <c r="I57" s="121">
         <f t="shared" si="13"/>
@@ -7090,11 +7116,11 @@
       </c>
       <c r="N57" s="107">
         <f>ROUND(SUM(G57:M57),0) + P57</f>
-        <v>380702.43</v>
+        <v>194889.43</v>
       </c>
       <c r="O57" s="135">
         <f t="shared" si="9"/>
-        <v>392123.43</v>
+        <v>200736.43</v>
       </c>
       <c r="P57" s="50">
         <f t="shared" si="8"/>
@@ -7117,11 +7143,10 @@
         <v>0.82</v>
       </c>
       <c r="E58" s="78">
-        <v>139730.44</v>
-      </c>
-      <c r="F58" s="79">
-        <f>E58</f>
-        <v>139730.44</v>
+        <v>200736.44</v>
+      </c>
+      <c r="F58" s="319">
+        <v>200736.44</v>
       </c>
       <c r="G58" s="80">
         <f t="shared" si="0"/>
@@ -7174,11 +7199,11 @@
         <v>1.34</v>
       </c>
       <c r="E59" s="78">
-        <v>294800.45</v>
-      </c>
-      <c r="F59" s="79">
+        <v>318478.45</v>
+      </c>
+      <c r="F59" s="319">
         <f>E59</f>
-        <v>294800.45</v>
+        <v>318478.45</v>
       </c>
       <c r="G59" s="80">
         <f t="shared" si="0"/>
@@ -7228,18 +7253,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E60" s="78">
-        <v>270492.46000000002</v>
+        <v>287298.46000000002</v>
       </c>
       <c r="F60" s="79">
         <v>250000</v>
       </c>
       <c r="G60" s="80">
         <f t="shared" si="0"/>
-        <v>20492.460000000021</v>
+        <v>37298.460000000021</v>
       </c>
       <c r="H60" s="80">
         <f t="shared" si="3"/>
-        <v>614.77380000000062</v>
+        <v>1118.9538000000007</v>
       </c>
       <c r="I60" s="120">
         <f t="shared" si="13"/>
@@ -7257,11 +7282,11 @@
       <c r="M60" s="141"/>
       <c r="N60" s="81">
         <f t="shared" si="6"/>
-        <v>287298.46000000002</v>
+        <v>304608.46000000002</v>
       </c>
       <c r="O60" s="134">
         <f t="shared" si="9"/>
-        <v>295917.46000000002</v>
+        <v>313746.46000000002</v>
       </c>
       <c r="P60" s="50">
         <f t="shared" si="8"/>
@@ -7284,14 +7309,14 @@
         <v>1.17</v>
       </c>
       <c r="E61" s="117">
-        <v>1508195.47</v>
+        <v>1921269.47</v>
       </c>
       <c r="F61" s="117">
         <v>0</v>
       </c>
       <c r="G61" s="118">
         <f t="shared" si="0"/>
-        <v>1508195.47</v>
+        <v>1921269.47</v>
       </c>
       <c r="H61" s="118"/>
       <c r="I61" s="123">
@@ -7312,11 +7337,11 @@
       </c>
       <c r="N61" s="119">
         <f t="shared" si="6"/>
-        <v>1921269.47</v>
+        <v>2334343.4700000002</v>
       </c>
       <c r="O61" s="136">
         <f t="shared" si="9"/>
-        <v>1978907.47</v>
+        <v>2404373.4700000002</v>
       </c>
       <c r="P61" s="50">
         <f t="shared" si="8"/>
@@ -7339,11 +7364,11 @@
         <v>1.35</v>
       </c>
       <c r="E62" s="79">
-        <v>305910.48</v>
+        <v>320854.48</v>
       </c>
       <c r="F62" s="79">
         <f>E62</f>
-        <v>305910.48</v>
+        <v>320854.48</v>
       </c>
       <c r="G62" s="106">
         <f t="shared" si="0"/>
@@ -7396,11 +7421,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E63" s="78">
-        <v>246400.49</v>
-      </c>
-      <c r="F63" s="79">
+        <v>266190.49</v>
+      </c>
+      <c r="F63" s="319">
         <f>E63</f>
-        <v>246400.49</v>
+        <v>266190.49</v>
       </c>
       <c r="G63" s="80">
         <f t="shared" si="0"/>
@@ -7450,16 +7475,19 @@
         <v>0.82</v>
       </c>
       <c r="E64" s="78">
-        <v>180400.5</v>
-      </c>
-      <c r="F64" s="79"/>
+        <v>380702.5</v>
+      </c>
+      <c r="F64" s="319">
+        <f>E64</f>
+        <v>380702.5</v>
+      </c>
       <c r="G64" s="80">
         <f t="shared" si="0"/>
-        <v>180400.5</v>
+        <v>0</v>
       </c>
       <c r="H64" s="80">
         <f t="shared" si="3"/>
-        <v>5412.0149999999994</v>
+        <v>0</v>
       </c>
       <c r="I64" s="120">
         <f t="shared" si="13"/>
@@ -7477,11 +7505,11 @@
       <c r="M64" s="141"/>
       <c r="N64" s="81">
         <f t="shared" si="6"/>
-        <v>380702.5</v>
+        <v>194889.5</v>
       </c>
       <c r="O64" s="134">
         <f t="shared" si="9"/>
-        <v>392123.5</v>
+        <v>200736.5</v>
       </c>
       <c r="P64" s="50">
         <f t="shared" si="8"/>
@@ -7501,11 +7529,11 @@
         <v>0.82</v>
       </c>
       <c r="E65" s="78">
-        <v>180400.51</v>
-      </c>
-      <c r="F65" s="79">
+        <v>194889.51</v>
+      </c>
+      <c r="F65" s="319">
         <f>E65</f>
-        <v>180400.51</v>
+        <v>194889.51</v>
       </c>
       <c r="G65" s="80">
         <f t="shared" si="0"/>
@@ -7555,11 +7583,11 @@
         <v>1.34</v>
       </c>
       <c r="E66" s="78">
-        <v>294800.52</v>
-      </c>
-      <c r="F66" s="79">
+        <v>318478.52</v>
+      </c>
+      <c r="F66" s="319">
         <f t="shared" ref="F66:F67" si="15">E66</f>
-        <v>294800.52</v>
+        <v>318478.52</v>
       </c>
       <c r="G66" s="80">
         <f t="shared" si="0"/>
@@ -7609,11 +7637,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E67" s="79">
-        <v>253792.53</v>
+        <v>266190.53000000003</v>
       </c>
       <c r="F67" s="79">
         <f t="shared" si="15"/>
-        <v>253792.53</v>
+        <v>266190.53000000003</v>
       </c>
       <c r="G67" s="80">
         <f t="shared" si="0"/>
@@ -7663,14 +7691,14 @@
         <v>1.17</v>
       </c>
       <c r="E68" s="78">
-        <v>257400.54</v>
-      </c>
-      <c r="F68" s="79">
-        <v>265122.53999999998</v>
+        <v>270352.53999999998</v>
+      </c>
+      <c r="F68" s="319">
+        <v>278463.53999999998</v>
       </c>
       <c r="G68" s="80">
         <f t="shared" si="0"/>
-        <v>-7721.9999999999709</v>
+        <v>-8111</v>
       </c>
       <c r="H68" s="80">
         <f t="shared" si="3"/>
@@ -7692,11 +7720,11 @@
       <c r="M68" s="141"/>
       <c r="N68" s="81">
         <f t="shared" si="6"/>
-        <v>270352.53999999998</v>
+        <v>269963.53999999998</v>
       </c>
       <c r="O68" s="134">
         <f t="shared" si="9"/>
-        <v>278463.53999999998</v>
+        <v>278062.53999999998</v>
       </c>
       <c r="P68" s="50">
         <f t="shared" si="8"/>
@@ -7716,11 +7744,11 @@
         <v>1.35</v>
       </c>
       <c r="E69" s="78">
-        <v>297000.55</v>
-      </c>
-      <c r="F69" s="79">
+        <v>320854.55</v>
+      </c>
+      <c r="F69" s="319">
         <f>E69</f>
-        <v>297000.55</v>
+        <v>320854.55</v>
       </c>
       <c r="G69" s="80">
         <f t="shared" si="0"/>
@@ -7770,18 +7798,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E70" s="78">
-        <v>789549.56</v>
-      </c>
-      <c r="F70" s="79">
-        <v>253792.56</v>
+        <v>818020.56</v>
+      </c>
+      <c r="F70" s="319">
+        <v>274176.56</v>
       </c>
       <c r="G70" s="80">
         <f t="shared" si="0"/>
-        <v>535757</v>
+        <v>543844</v>
       </c>
       <c r="H70" s="80">
         <f t="shared" si="3"/>
-        <v>16072.71</v>
+        <v>16315.32</v>
       </c>
       <c r="I70" s="120">
         <f t="shared" si="13"/>
@@ -7799,11 +7827,11 @@
       <c r="M70" s="141"/>
       <c r="N70" s="81">
         <f t="shared" si="6"/>
-        <v>818020.56</v>
+        <v>826350.56</v>
       </c>
       <c r="O70" s="134">
         <f t="shared" si="9"/>
-        <v>842561.56</v>
+        <v>851141.56</v>
       </c>
       <c r="P70" s="50">
         <f t="shared" si="8"/>
@@ -7823,11 +7851,11 @@
         <v>0.82</v>
       </c>
       <c r="E71" s="78">
-        <v>180400.57</v>
+        <v>194889.57</v>
       </c>
       <c r="F71" s="79">
         <f>E71</f>
-        <v>180400.57</v>
+        <v>194889.57</v>
       </c>
       <c r="G71" s="80">
         <f t="shared" si="0"/>
@@ -7880,11 +7908,11 @@
         <v>0.82</v>
       </c>
       <c r="E72" s="78">
-        <v>180400.58</v>
-      </c>
-      <c r="F72" s="79">
+        <v>194889.58</v>
+      </c>
+      <c r="F72" s="319">
         <f t="shared" ref="F72" si="16">E72</f>
-        <v>180400.58</v>
+        <v>194889.58</v>
       </c>
       <c r="G72" s="80">
         <f t="shared" si="0"/>
@@ -7937,15 +7965,15 @@
         <v>1.34</v>
       </c>
       <c r="E73" s="79">
-        <v>286569.59000000003</v>
-      </c>
-      <c r="F73" s="79">
-        <f>339888.53</f>
-        <v>339888.53</v>
+        <v>265159.59000000003</v>
+      </c>
+      <c r="F73" s="319">
+        <f>E73</f>
+        <v>265159.59000000003</v>
       </c>
       <c r="G73" s="106">
         <f t="shared" si="0"/>
-        <v>-53318.94</v>
+        <v>0</v>
       </c>
       <c r="H73" s="106">
         <f t="shared" si="3"/>
@@ -7967,11 +7995,11 @@
       <c r="M73" s="142"/>
       <c r="N73" s="81">
         <f t="shared" si="6"/>
-        <v>265159.59000000003</v>
+        <v>318478.59000000003</v>
       </c>
       <c r="O73" s="135">
         <f t="shared" si="9"/>
-        <v>273114.59000000003</v>
+        <v>328032.59000000003</v>
       </c>
       <c r="P73" s="50">
         <f t="shared" si="8"/>
@@ -7991,11 +8019,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E74" s="78">
-        <v>239520.6</v>
-      </c>
-      <c r="F74" s="79">
+        <v>266190.59999999998</v>
+      </c>
+      <c r="F74" s="319">
         <f>E74</f>
-        <v>239520.6</v>
+        <v>266190.59999999998</v>
       </c>
       <c r="G74" s="80">
         <f t="shared" si="0"/>
@@ -8045,11 +8073,11 @@
         <v>1.17</v>
       </c>
       <c r="E75" s="78">
-        <v>257400.61</v>
-      </c>
-      <c r="F75" s="79">
+        <v>278074.61</v>
+      </c>
+      <c r="F75" s="319">
         <f>E75</f>
-        <v>257400.61</v>
+        <v>278074.61</v>
       </c>
       <c r="G75" s="80">
         <f t="shared" si="0"/>
@@ -8099,11 +8127,11 @@
         <v>1.35</v>
       </c>
       <c r="E76" s="78">
-        <v>297000.62</v>
-      </c>
-      <c r="F76" s="79">
+        <v>320854.62</v>
+      </c>
+      <c r="F76" s="319">
         <f>E76</f>
-        <v>297000.62</v>
+        <v>320854.62</v>
       </c>
       <c r="G76" s="80">
         <f t="shared" si="0"/>
@@ -8153,11 +8181,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E77" s="78">
-        <v>246400.63</v>
-      </c>
-      <c r="F77" s="79">
+        <v>266190.63</v>
+      </c>
+      <c r="F77" s="319">
         <f>E77</f>
-        <v>246400.63</v>
+        <v>266190.63</v>
       </c>
       <c r="G77" s="80">
         <f t="shared" si="0"/>
@@ -8210,14 +8238,14 @@
         <v>0.82</v>
       </c>
       <c r="E78" s="78">
-        <v>188261.64</v>
-      </c>
-      <c r="F78" s="79">
-        <v>193909.64</v>
+        <v>189241.64</v>
+      </c>
+      <c r="F78" s="319">
+        <v>194918.64</v>
       </c>
       <c r="G78" s="80">
         <f t="shared" si="0"/>
-        <v>-5648</v>
+        <v>-5677</v>
       </c>
       <c r="H78" s="80">
         <f t="shared" si="3"/>
@@ -8239,11 +8267,11 @@
       <c r="M78" s="141"/>
       <c r="N78" s="81">
         <f t="shared" si="6"/>
-        <v>189241.64</v>
+        <v>189212.64</v>
       </c>
       <c r="O78" s="134">
         <f t="shared" si="9"/>
-        <v>194918.64</v>
+        <v>194888.64</v>
       </c>
       <c r="P78" s="50">
         <f t="shared" si="8"/>
@@ -8263,18 +8291,18 @@
         <v>0.82</v>
       </c>
       <c r="E79" s="79">
-        <v>424018.65</v>
+        <v>343228.65</v>
       </c>
       <c r="F79" s="218">
         <v>280000.65000000002</v>
       </c>
       <c r="G79" s="106">
         <f t="shared" ref="G79:G117" si="17">E79-F79</f>
-        <v>144018</v>
+        <v>63228</v>
       </c>
       <c r="H79" s="106">
         <f t="shared" si="3"/>
-        <v>4320.54</v>
+        <v>1896.84</v>
       </c>
       <c r="I79" s="121">
         <f t="shared" ref="I79:I110" si="18">J$2*D79/100</f>
@@ -8292,11 +8320,11 @@
       <c r="M79" s="142"/>
       <c r="N79" s="81">
         <f t="shared" si="6"/>
-        <v>343228.65</v>
+        <v>260014.65</v>
       </c>
       <c r="O79" s="135">
         <f t="shared" si="9"/>
-        <v>353525.65</v>
+        <v>267814.65000000002</v>
       </c>
       <c r="P79" s="50">
         <f t="shared" si="8"/>
@@ -8319,18 +8347,18 @@
         <v>1.34</v>
       </c>
       <c r="E80" s="79">
-        <v>1208976.6599999999</v>
+        <v>1563724.66</v>
       </c>
       <c r="F80" s="79">
         <v>0</v>
       </c>
       <c r="G80" s="106">
         <f t="shared" si="17"/>
-        <v>1208976.6599999999</v>
+        <v>1563724.66</v>
       </c>
       <c r="H80" s="106">
         <f t="shared" ref="H80:H117" si="20">IF(G80&gt;0,G80*3%,0)</f>
-        <v>36269.299799999993</v>
+        <v>46911.739799999996</v>
       </c>
       <c r="I80" s="121">
         <f t="shared" si="18"/>
@@ -8348,11 +8376,11 @@
       <c r="M80" s="142"/>
       <c r="N80" s="107">
         <f t="shared" si="6"/>
-        <v>1563724.66</v>
+        <v>1929114.66</v>
       </c>
       <c r="O80" s="135">
         <f t="shared" si="9"/>
-        <v>1610636.66</v>
+        <v>1986987.66</v>
       </c>
       <c r="P80" s="50">
         <f t="shared" si="8"/>
@@ -8372,15 +8400,15 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E81" s="78">
-        <v>454185.67</v>
-      </c>
-      <c r="F81" s="79">
-        <f>200000+261811.67+5877</f>
-        <v>467688.67000000004</v>
+        <v>260268.67</v>
+      </c>
+      <c r="F81" s="319">
+        <f>E81</f>
+        <v>260268.67</v>
       </c>
       <c r="G81" s="80">
         <f t="shared" si="17"/>
-        <v>-13503.000000000058</v>
+        <v>0</v>
       </c>
       <c r="H81" s="80">
         <f t="shared" si="20"/>
@@ -8402,11 +8430,11 @@
       <c r="M81" s="141"/>
       <c r="N81" s="81">
         <f t="shared" ref="N81:N117" si="22">ROUND(SUM(G81:M81),0) + P81</f>
-        <v>252687.67</v>
+        <v>266190.67</v>
       </c>
       <c r="O81" s="134">
         <f t="shared" si="9"/>
-        <v>260268.67</v>
+        <v>274176.67</v>
       </c>
       <c r="P81" s="50">
         <f t="shared" si="8"/>
@@ -8426,18 +8454,18 @@
         <v>1.17</v>
       </c>
       <c r="E82" s="186">
-        <v>8488408.6799999997</v>
+        <v>9116135.6799999997</v>
       </c>
       <c r="F82" s="186">
         <v>0</v>
       </c>
       <c r="G82" s="187">
         <f t="shared" si="17"/>
-        <v>8488408.6799999997</v>
+        <v>9116135.6799999997</v>
       </c>
       <c r="H82" s="187">
         <f t="shared" si="20"/>
-        <v>254652.26039999997</v>
+        <v>273484.07039999997</v>
       </c>
       <c r="I82" s="188">
         <f t="shared" si="18"/>
@@ -8457,11 +8485,11 @@
       <c r="M82" s="189"/>
       <c r="N82" s="190">
         <f t="shared" si="22"/>
-        <v>9116135.6799999997</v>
+        <v>9762694.6799999997</v>
       </c>
       <c r="O82" s="191">
         <f t="shared" si="9"/>
-        <v>9389619.6799999997</v>
+        <v>10055575.68</v>
       </c>
       <c r="P82" s="50">
         <f t="shared" si="8"/>
@@ -8481,14 +8509,14 @@
         <v>1.35</v>
       </c>
       <c r="E83" s="78">
-        <v>295421.69</v>
-      </c>
-      <c r="F83" s="79">
-        <v>300000</v>
+        <v>316276.69</v>
+      </c>
+      <c r="F83" s="319">
+        <v>316500</v>
       </c>
       <c r="G83" s="80">
         <f t="shared" si="17"/>
-        <v>-4578.3099999999977</v>
+        <v>-223.30999999999767</v>
       </c>
       <c r="H83" s="80">
         <f t="shared" si="20"/>
@@ -8512,11 +8540,11 @@
       <c r="M83" s="141"/>
       <c r="N83" s="81">
         <f t="shared" si="22"/>
-        <v>316276.69</v>
+        <v>320631.69</v>
       </c>
       <c r="O83" s="134">
         <f t="shared" si="9"/>
-        <v>325764.69</v>
+        <v>330250.69</v>
       </c>
       <c r="P83" s="50">
         <f t="shared" si="8"/>
@@ -8536,16 +8564,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E84" s="79">
-        <v>650623.69999999995</v>
+        <v>936333.7</v>
       </c>
       <c r="F84" s="79"/>
       <c r="G84" s="106">
         <f t="shared" si="17"/>
-        <v>650623.69999999995</v>
+        <v>936333.7</v>
       </c>
       <c r="H84" s="106">
         <f t="shared" si="20"/>
-        <v>19518.710999999999</v>
+        <v>28090.010999999999</v>
       </c>
       <c r="I84" s="121">
         <f t="shared" si="18"/>
@@ -8563,11 +8591,11 @@
       <c r="M84" s="142"/>
       <c r="N84" s="81">
         <f t="shared" si="22"/>
-        <v>936333.7</v>
+        <v>1230614.7</v>
       </c>
       <c r="O84" s="135">
         <f t="shared" si="9"/>
-        <v>964423.7</v>
+        <v>1267532.7</v>
       </c>
       <c r="P84" s="50">
         <f t="shared" si="8"/>
@@ -8590,11 +8618,11 @@
         <v>0.82</v>
       </c>
       <c r="E85" s="78">
-        <v>180400.71</v>
-      </c>
-      <c r="F85" s="79">
+        <v>194889.71</v>
+      </c>
+      <c r="F85" s="319">
         <f>E85</f>
-        <v>180400.71</v>
+        <v>194889.71</v>
       </c>
       <c r="G85" s="80">
         <f t="shared" si="17"/>
@@ -8644,11 +8672,11 @@
         <v>0.82</v>
       </c>
       <c r="E86" s="78">
-        <v>180400.72</v>
-      </c>
-      <c r="F86" s="79">
+        <v>194889.72</v>
+      </c>
+      <c r="F86" s="319">
         <f>E86</f>
-        <v>180400.72</v>
+        <v>194889.72</v>
       </c>
       <c r="G86" s="80">
         <f t="shared" si="17"/>
@@ -8698,16 +8726,16 @@
         <v>1.34</v>
       </c>
       <c r="E87" s="78">
-        <v>294800.73</v>
+        <v>622123.73</v>
       </c>
       <c r="F87" s="79"/>
       <c r="G87" s="80">
         <f t="shared" si="17"/>
-        <v>294800.73</v>
+        <v>622123.73</v>
       </c>
       <c r="H87" s="80">
         <f t="shared" si="20"/>
-        <v>8844.0218999999997</v>
+        <v>18663.711899999998</v>
       </c>
       <c r="I87" s="120">
         <f t="shared" si="18"/>
@@ -8725,11 +8753,11 @@
       <c r="M87" s="141"/>
       <c r="N87" s="81">
         <f t="shared" si="22"/>
-        <v>622123.73</v>
+        <v>959265.73</v>
       </c>
       <c r="O87" s="134">
         <f t="shared" si="9"/>
-        <v>640787.73</v>
+        <v>988043.73</v>
       </c>
       <c r="P87" s="50">
         <f t="shared" si="8"/>
@@ -8749,11 +8777,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E88" s="117">
-        <v>376400.74</v>
-      </c>
-      <c r="F88" s="117">
+        <v>408076.74</v>
+      </c>
+      <c r="F88" s="320">
         <f>E88</f>
-        <v>376400.74</v>
+        <v>408076.74</v>
       </c>
       <c r="G88" s="118">
         <f t="shared" si="17"/>
@@ -8791,7 +8819,7 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="Q88" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.3">
@@ -8807,14 +8835,14 @@
         <v>1.17</v>
       </c>
       <c r="E89" s="78">
-        <v>250219.75</v>
-      </c>
-      <c r="F89" s="79">
-        <v>257726.75</v>
+        <v>270567.75</v>
+      </c>
+      <c r="F89" s="319">
+        <v>278684.75</v>
       </c>
       <c r="G89" s="80">
         <f t="shared" si="17"/>
-        <v>-7507</v>
+        <v>-8117</v>
       </c>
       <c r="H89" s="80">
         <f t="shared" si="20"/>
@@ -8836,11 +8864,11 @@
       <c r="M89" s="141"/>
       <c r="N89" s="81">
         <f t="shared" si="22"/>
-        <v>270567.75</v>
+        <v>269957.75</v>
       </c>
       <c r="O89" s="134">
         <f t="shared" si="9"/>
-        <v>278684.75</v>
+        <v>278056.75</v>
       </c>
       <c r="P89" s="50">
         <f t="shared" si="8"/>
@@ -8860,19 +8888,18 @@
         <v>1.35</v>
       </c>
       <c r="E90" s="79">
-        <v>297000.76</v>
-      </c>
-      <c r="F90" s="79">
-        <f t="shared" ref="F90:F96" si="23">E90</f>
-        <v>297000.76</v>
+        <v>330480.76</v>
+      </c>
+      <c r="F90" s="319">
+        <v>320854.76</v>
       </c>
       <c r="G90" s="106">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9626</v>
       </c>
       <c r="H90" s="106">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>288.77999999999997</v>
       </c>
       <c r="I90" s="121">
         <f t="shared" si="18"/>
@@ -8890,11 +8917,11 @@
       <c r="M90" s="142"/>
       <c r="N90" s="107">
         <f t="shared" si="22"/>
-        <v>320854.76</v>
+        <v>330769.76</v>
       </c>
       <c r="O90" s="135">
         <f t="shared" si="9"/>
-        <v>330480.76</v>
+        <v>340692.76</v>
       </c>
       <c r="P90" s="50">
         <f t="shared" si="8"/>
@@ -8914,11 +8941,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="78">
-        <v>246400.77</v>
-      </c>
-      <c r="F91" s="79">
-        <f t="shared" si="23"/>
-        <v>246400.77</v>
+        <v>266190.77</v>
+      </c>
+      <c r="F91" s="319">
+        <f t="shared" ref="F90:F96" si="23">E91</f>
+        <v>266190.77</v>
       </c>
       <c r="G91" s="80">
         <f t="shared" si="17"/>
@@ -8968,15 +8995,15 @@
         <v>0.82</v>
       </c>
       <c r="E92" s="117">
-        <v>355762.78</v>
-      </c>
-      <c r="F92" s="117">
-        <f t="shared" si="23"/>
-        <v>355762.78</v>
+        <v>370686.78</v>
+      </c>
+      <c r="F92" s="320">
+        <f>255000+370686.78</f>
+        <v>625686.78</v>
       </c>
       <c r="G92" s="118">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-255000</v>
       </c>
       <c r="H92" s="118"/>
       <c r="I92" s="123">
@@ -8997,18 +9024,18 @@
       </c>
       <c r="N92" s="119">
         <f t="shared" si="22"/>
-        <v>359889.78</v>
+        <v>104889.78</v>
       </c>
       <c r="O92" s="136">
         <f t="shared" si="9"/>
-        <v>370686.78</v>
+        <v>108036.78</v>
       </c>
       <c r="P92" s="50">
         <f t="shared" si="8"/>
         <v>0.78000000000000047</v>
       </c>
       <c r="Q92" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.3">
@@ -9024,11 +9051,11 @@
         <v>0.82</v>
       </c>
       <c r="E93" s="78">
-        <v>193069.79</v>
-      </c>
-      <c r="F93" s="79">
+        <v>194889.79</v>
+      </c>
+      <c r="F93" s="319">
         <f t="shared" si="23"/>
-        <v>193069.79</v>
+        <v>194889.79</v>
       </c>
       <c r="G93" s="80">
         <f t="shared" si="17"/>
@@ -9081,11 +9108,11 @@
         <v>1.34</v>
       </c>
       <c r="E94" s="79">
-        <v>294800.8</v>
-      </c>
-      <c r="F94" s="79">
+        <v>318478.8</v>
+      </c>
+      <c r="F94" s="319">
         <f t="shared" si="23"/>
-        <v>294800.8</v>
+        <v>318478.8</v>
       </c>
       <c r="G94" s="80">
         <f>E94-F94</f>
@@ -9135,11 +9162,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E95" s="79">
-        <v>246400.81</v>
-      </c>
-      <c r="F95" s="79">
+        <v>266190.81</v>
+      </c>
+      <c r="F95" s="319">
         <f t="shared" si="23"/>
-        <v>246400.81</v>
+        <v>266190.81</v>
       </c>
       <c r="G95" s="106">
         <f t="shared" si="17"/>
@@ -9192,11 +9219,11 @@
         <v>1.17</v>
       </c>
       <c r="E96" s="78">
-        <v>276018.82</v>
-      </c>
-      <c r="F96" s="79">
+        <v>278074.82</v>
+      </c>
+      <c r="F96" s="319">
         <f t="shared" si="23"/>
-        <v>276018.82</v>
+        <v>278074.82</v>
       </c>
       <c r="G96" s="80">
         <f t="shared" si="17"/>
@@ -9246,15 +9273,14 @@
         <v>1.35</v>
       </c>
       <c r="E97" s="79">
-        <v>297000.83</v>
-      </c>
-      <c r="F97" s="79">
-        <f t="shared" ref="F97:F104" si="24">E97</f>
-        <v>297000.83</v>
+        <v>320854.83</v>
+      </c>
+      <c r="F97" s="319">
+        <v>330480.83</v>
       </c>
       <c r="G97" s="80">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-9626</v>
       </c>
       <c r="H97" s="80">
         <f t="shared" si="20"/>
@@ -9276,11 +9302,11 @@
       <c r="M97" s="141"/>
       <c r="N97" s="81">
         <f t="shared" si="22"/>
-        <v>320854.83</v>
+        <v>311228.83</v>
       </c>
       <c r="O97" s="134">
         <f t="shared" si="9"/>
-        <v>330480.83</v>
+        <v>320565.83</v>
       </c>
       <c r="P97" s="50">
         <f t="shared" si="8"/>
@@ -9300,16 +9326,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E98" s="79">
-        <v>246400.84</v>
+        <v>519983.84</v>
       </c>
       <c r="F98" s="79"/>
       <c r="G98" s="80">
         <f t="shared" si="17"/>
-        <v>246400.84</v>
+        <v>519983.84</v>
       </c>
       <c r="H98" s="80">
         <f t="shared" si="20"/>
-        <v>7392.0252</v>
+        <v>15599.5152</v>
       </c>
       <c r="I98" s="120">
         <f t="shared" si="18"/>
@@ -9327,14 +9353,14 @@
       <c r="M98" s="141"/>
       <c r="N98" s="81">
         <f t="shared" si="22"/>
-        <v>519983.84</v>
+        <v>801774.84</v>
       </c>
       <c r="O98" s="134">
         <f t="shared" si="9"/>
-        <v>535583.84000000008</v>
+        <v>825827.83999999997</v>
       </c>
       <c r="P98" s="50">
-        <f t="shared" ref="P98:P117" si="25">P97+0.01</f>
+        <f t="shared" ref="P98:P117" si="24">P97+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
@@ -9351,11 +9377,11 @@
         <v>0.82</v>
       </c>
       <c r="E99" s="78">
-        <v>180400.85</v>
-      </c>
-      <c r="F99" s="79">
-        <f t="shared" si="24"/>
-        <v>180400.85</v>
+        <v>194889.85</v>
+      </c>
+      <c r="F99" s="319">
+        <f t="shared" ref="F97:F104" si="25">E99</f>
+        <v>194889.85</v>
       </c>
       <c r="G99" s="80">
         <f t="shared" si="17"/>
@@ -9388,7 +9414,7 @@
         <v>200736.85</v>
       </c>
       <c r="P99" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.85000000000000053</v>
       </c>
     </row>
@@ -9405,11 +9431,11 @@
         <v>0.82</v>
       </c>
       <c r="E100" s="79">
-        <v>180400.86</v>
-      </c>
-      <c r="F100" s="79">
-        <f t="shared" si="24"/>
-        <v>180400.86</v>
+        <v>194889.86</v>
+      </c>
+      <c r="F100" s="319">
+        <f t="shared" si="25"/>
+        <v>194889.86</v>
       </c>
       <c r="G100" s="106">
         <f t="shared" si="17"/>
@@ -9442,7 +9468,7 @@
         <v>200736.86</v>
       </c>
       <c r="P100" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
@@ -9459,11 +9485,11 @@
         <v>1.34</v>
       </c>
       <c r="E101" s="78">
-        <v>294800.87</v>
-      </c>
-      <c r="F101" s="79">
-        <f t="shared" si="24"/>
-        <v>294800.87</v>
+        <v>318478.87</v>
+      </c>
+      <c r="F101" s="319">
+        <f t="shared" si="25"/>
+        <v>318478.87</v>
       </c>
       <c r="G101" s="80">
         <f t="shared" si="17"/>
@@ -9496,7 +9522,7 @@
         <v>328032.87</v>
       </c>
       <c r="P101" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.87000000000000055</v>
       </c>
     </row>
@@ -9513,11 +9539,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E102" s="78">
-        <v>246400.88</v>
-      </c>
-      <c r="F102" s="79">
-        <f t="shared" si="24"/>
-        <v>246400.88</v>
+        <v>266190.88</v>
+      </c>
+      <c r="F102" s="319">
+        <f t="shared" si="25"/>
+        <v>266190.88</v>
       </c>
       <c r="G102" s="80">
         <f t="shared" si="17"/>
@@ -9550,7 +9576,7 @@
         <v>274176.88</v>
       </c>
       <c r="P102" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.88000000000000056</v>
       </c>
     </row>
@@ -9567,11 +9593,11 @@
         <v>1.17</v>
       </c>
       <c r="E103" s="78">
-        <v>257400.89</v>
-      </c>
-      <c r="F103" s="79">
-        <f t="shared" si="24"/>
-        <v>257400.89</v>
+        <v>278074.89</v>
+      </c>
+      <c r="F103" s="319">
+        <f t="shared" si="25"/>
+        <v>278074.89</v>
       </c>
       <c r="G103" s="80">
         <f t="shared" si="17"/>
@@ -9604,7 +9630,7 @@
         <v>286416.89</v>
       </c>
       <c r="P103" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.89000000000000057</v>
       </c>
     </row>
@@ -9621,11 +9647,11 @@
         <v>0.1</v>
       </c>
       <c r="E104" s="78">
-        <v>22000.9</v>
-      </c>
-      <c r="F104" s="79">
-        <f t="shared" si="24"/>
-        <v>22000.9</v>
+        <v>23767.9</v>
+      </c>
+      <c r="F104" s="319">
+        <f t="shared" si="25"/>
+        <v>23767.9</v>
       </c>
       <c r="G104" s="80">
         <f t="shared" si="17"/>
@@ -9658,7 +9684,7 @@
         <v>24480.9</v>
       </c>
       <c r="P104" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.90000000000000058</v>
       </c>
     </row>
@@ -9675,11 +9701,11 @@
         <v>0.1</v>
       </c>
       <c r="E105" s="78">
-        <v>23591.91</v>
-      </c>
-      <c r="F105" s="79">
+        <v>23767.91</v>
+      </c>
+      <c r="F105" s="319">
         <f>E105</f>
-        <v>23591.91</v>
+        <v>23767.91</v>
       </c>
       <c r="G105" s="80">
         <f t="shared" si="17"/>
@@ -9712,7 +9738,7 @@
         <v>24480.91</v>
       </c>
       <c r="P105" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
@@ -9729,14 +9755,15 @@
         <v>0.1</v>
       </c>
       <c r="E106" s="78">
-        <v>21394.92</v>
-      </c>
-      <c r="F106" s="79">
-        <v>22036.92</v>
+        <v>23819.919999999998</v>
+      </c>
+      <c r="F106" s="319">
+        <f>E106</f>
+        <v>23819.919999999998</v>
       </c>
       <c r="G106" s="80">
         <f t="shared" si="17"/>
-        <v>-642</v>
+        <v>0</v>
       </c>
       <c r="H106" s="80">
         <f t="shared" si="20"/>
@@ -9758,14 +9785,14 @@
       <c r="M106" s="141"/>
       <c r="N106" s="81">
         <f t="shared" si="22"/>
-        <v>23125.919999999998</v>
+        <v>23767.919999999998</v>
       </c>
       <c r="O106" s="134">
         <f t="shared" si="26"/>
-        <v>23819.919999999998</v>
+        <v>24480.92</v>
       </c>
       <c r="P106" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
@@ -9782,11 +9809,11 @@
         <v>0.1</v>
       </c>
       <c r="E107" s="79">
-        <v>22000.93</v>
-      </c>
-      <c r="F107" s="79">
+        <v>23767.93</v>
+      </c>
+      <c r="F107" s="319">
         <f>E107</f>
-        <v>22000.93</v>
+        <v>23767.93</v>
       </c>
       <c r="G107" s="106">
         <f t="shared" si="17"/>
@@ -9819,7 +9846,7 @@
         <v>24480.93</v>
       </c>
       <c r="P107" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
@@ -9836,11 +9863,11 @@
         <v>0.1</v>
       </c>
       <c r="E108" s="79">
-        <v>22000.94</v>
-      </c>
-      <c r="F108" s="79">
+        <v>23767.94</v>
+      </c>
+      <c r="F108" s="319">
         <f t="shared" ref="F108:F113" si="28">E108</f>
-        <v>22000.94</v>
+        <v>23767.94</v>
       </c>
       <c r="G108" s="106">
         <f t="shared" si="17"/>
@@ -9873,7 +9900,7 @@
         <v>24480.94</v>
       </c>
       <c r="P108" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.94000000000000061</v>
       </c>
     </row>
@@ -9890,11 +9917,11 @@
         <v>0.1</v>
       </c>
       <c r="E109" s="79">
-        <v>22000.95</v>
-      </c>
-      <c r="F109" s="79">
+        <v>23767.95</v>
+      </c>
+      <c r="F109" s="319">
         <f t="shared" si="28"/>
-        <v>22000.95</v>
+        <v>23767.95</v>
       </c>
       <c r="G109" s="106">
         <f t="shared" si="17"/>
@@ -9927,7 +9954,7 @@
         <v>24480.95</v>
       </c>
       <c r="P109" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.95000000000000062</v>
       </c>
     </row>
@@ -9944,11 +9971,11 @@
         <v>0.1</v>
       </c>
       <c r="E110" s="79">
-        <v>22000.959999999999</v>
-      </c>
-      <c r="F110" s="79">
+        <v>23767.96</v>
+      </c>
+      <c r="F110" s="319">
         <f>E110</f>
-        <v>22000.959999999999</v>
+        <v>23767.96</v>
       </c>
       <c r="G110" s="106">
         <f t="shared" si="17"/>
@@ -9981,7 +10008,7 @@
         <v>24480.959999999999</v>
       </c>
       <c r="P110" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.96000000000000063</v>
       </c>
       <c r="Q110" t="s">
@@ -10001,11 +10028,11 @@
         <v>0.1</v>
       </c>
       <c r="E111" s="79">
-        <v>22000.97</v>
-      </c>
-      <c r="F111" s="79">
+        <v>23767.97</v>
+      </c>
+      <c r="F111" s="319">
         <f t="shared" si="28"/>
-        <v>22000.97</v>
+        <v>23767.97</v>
       </c>
       <c r="G111" s="106">
         <f t="shared" si="17"/>
@@ -10038,7 +10065,7 @@
         <v>24480.97</v>
       </c>
       <c r="P111" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.97000000000000064</v>
       </c>
     </row>
@@ -10055,11 +10082,11 @@
         <v>0.1</v>
       </c>
       <c r="E112" s="79">
-        <v>22000.98</v>
-      </c>
-      <c r="F112" s="79">
+        <v>23767.98</v>
+      </c>
+      <c r="F112" s="319">
         <f>E112</f>
-        <v>22000.98</v>
+        <v>23767.98</v>
       </c>
       <c r="G112" s="106">
         <f t="shared" si="17"/>
@@ -10092,7 +10119,7 @@
         <v>24480.98</v>
       </c>
       <c r="P112" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.98000000000000065</v>
       </c>
     </row>
@@ -10109,11 +10136,11 @@
         <v>0.1</v>
       </c>
       <c r="E113" s="79">
-        <v>22000.99</v>
-      </c>
-      <c r="F113" s="79">
+        <v>23767.99</v>
+      </c>
+      <c r="F113" s="319">
         <f t="shared" si="28"/>
-        <v>22000.99</v>
+        <v>23767.99</v>
       </c>
       <c r="G113" s="106">
         <f t="shared" si="17"/>
@@ -10146,7 +10173,7 @@
         <v>24480.99</v>
       </c>
       <c r="P113" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.99000000000000066</v>
       </c>
     </row>
@@ -10163,12 +10190,15 @@
         <v>0.1</v>
       </c>
       <c r="E114" s="79">
-        <v>-4806</v>
-      </c>
-      <c r="F114" s="79"/>
+        <v>18962</v>
+      </c>
+      <c r="F114" s="319">
+        <f>E114</f>
+        <v>18962</v>
+      </c>
       <c r="G114" s="106">
         <f t="shared" si="17"/>
-        <v>-4806</v>
+        <v>0</v>
       </c>
       <c r="H114" s="106">
         <f t="shared" si="20"/>
@@ -10190,14 +10220,14 @@
       <c r="M114" s="142"/>
       <c r="N114" s="81">
         <f t="shared" si="22"/>
-        <v>18962</v>
+        <v>23768</v>
       </c>
       <c r="O114" s="135">
         <f t="shared" si="26"/>
-        <v>19531</v>
+        <v>24481</v>
       </c>
       <c r="P114" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
@@ -10214,11 +10244,11 @@
         <v>0.1</v>
       </c>
       <c r="E115" s="79">
-        <v>22001.01</v>
-      </c>
-      <c r="F115" s="79">
+        <v>23768.01</v>
+      </c>
+      <c r="F115" s="319">
         <f>E115</f>
-        <v>22001.01</v>
+        <v>23768.01</v>
       </c>
       <c r="G115" s="106">
         <f t="shared" si="17"/>
@@ -10251,7 +10281,7 @@
         <v>24481.01</v>
       </c>
       <c r="P115" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
@@ -10268,11 +10298,11 @@
         <v>0.1</v>
       </c>
       <c r="E116" s="79">
-        <v>22001.02</v>
-      </c>
-      <c r="F116" s="79">
+        <v>23768.02</v>
+      </c>
+      <c r="F116" s="319">
         <f>E116</f>
-        <v>22001.02</v>
+        <v>23768.02</v>
       </c>
       <c r="G116" s="106">
         <f t="shared" si="17"/>
@@ -10305,7 +10335,7 @@
         <v>24481.02</v>
       </c>
       <c r="P116" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
@@ -10322,11 +10352,11 @@
         <v>0.1</v>
       </c>
       <c r="E117" s="79">
-        <v>22001.03</v>
-      </c>
-      <c r="F117" s="79">
+        <v>23768.03</v>
+      </c>
+      <c r="F117" s="319">
         <f>E117</f>
-        <v>22001.03</v>
+        <v>23768.03</v>
       </c>
       <c r="G117" s="106">
         <f t="shared" si="17"/>
@@ -10359,7 +10389,7 @@
         <v>24481.03</v>
       </c>
       <c r="P117" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
@@ -10391,19 +10421,19 @@
       </c>
       <c r="E119" s="130">
         <f t="shared" si="31"/>
-        <v>47168728.960000001</v>
+        <v>52939530.560000002</v>
       </c>
       <c r="F119" s="213">
         <f>SUM(F15:F118)</f>
-        <v>20030676.670000002</v>
+        <v>24414829.380000003</v>
       </c>
       <c r="G119" s="131">
         <f t="shared" si="31"/>
-        <v>27138052.289999999</v>
+        <v>28524701.18</v>
       </c>
       <c r="H119" s="131">
         <f t="shared" si="31"/>
-        <v>737556.28410000005</v>
+        <v>785634.52439999999</v>
       </c>
       <c r="I119" s="132">
         <f t="shared" si="31"/>
@@ -10418,11 +10448,11 @@
       <c r="M119" s="144"/>
       <c r="N119" s="140">
         <f t="shared" si="31"/>
-        <v>52861973.560000002</v>
+        <v>53986697.560000002</v>
       </c>
       <c r="O119" s="137">
         <f t="shared" si="31"/>
-        <v>54447842.560000002</v>
+        <v>55606304.559999995</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10431,96 +10461,96 @@
     </row>
     <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="269" t="s">
+      <c r="B122" s="287" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="269"/>
-      <c r="D122" s="269"/>
-      <c r="E122" s="269"/>
-      <c r="F122" s="269"/>
-      <c r="G122" s="269"/>
-      <c r="H122" s="269"/>
-      <c r="I122" s="269"/>
-      <c r="J122" s="269"/>
-      <c r="K122" s="269"/>
-      <c r="L122" s="269"/>
-      <c r="M122" s="269"/>
-      <c r="N122" s="269"/>
+      <c r="C122" s="287"/>
+      <c r="D122" s="287"/>
+      <c r="E122" s="287"/>
+      <c r="F122" s="287"/>
+      <c r="G122" s="287"/>
+      <c r="H122" s="287"/>
+      <c r="I122" s="287"/>
+      <c r="J122" s="287"/>
+      <c r="K122" s="287"/>
+      <c r="L122" s="287"/>
+      <c r="M122" s="287"/>
+      <c r="N122" s="287"/>
     </row>
     <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="269"/>
-      <c r="C123" s="269"/>
-      <c r="D123" s="269"/>
-      <c r="E123" s="269"/>
-      <c r="F123" s="269"/>
-      <c r="G123" s="269"/>
-      <c r="H123" s="269"/>
-      <c r="I123" s="269"/>
-      <c r="J123" s="269"/>
-      <c r="K123" s="269"/>
-      <c r="L123" s="269"/>
-      <c r="M123" s="269"/>
-      <c r="N123" s="269"/>
+      <c r="B123" s="287"/>
+      <c r="C123" s="287"/>
+      <c r="D123" s="287"/>
+      <c r="E123" s="287"/>
+      <c r="F123" s="287"/>
+      <c r="G123" s="287"/>
+      <c r="H123" s="287"/>
+      <c r="I123" s="287"/>
+      <c r="J123" s="287"/>
+      <c r="K123" s="287"/>
+      <c r="L123" s="287"/>
+      <c r="M123" s="287"/>
+      <c r="N123" s="287"/>
     </row>
     <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="269"/>
-      <c r="C124" s="269"/>
-      <c r="D124" s="269"/>
-      <c r="E124" s="269"/>
-      <c r="F124" s="269"/>
-      <c r="G124" s="269"/>
-      <c r="H124" s="269"/>
-      <c r="I124" s="269"/>
-      <c r="J124" s="269"/>
-      <c r="K124" s="269"/>
-      <c r="L124" s="269"/>
-      <c r="M124" s="269"/>
-      <c r="N124" s="269"/>
+      <c r="B124" s="287"/>
+      <c r="C124" s="287"/>
+      <c r="D124" s="287"/>
+      <c r="E124" s="287"/>
+      <c r="F124" s="287"/>
+      <c r="G124" s="287"/>
+      <c r="H124" s="287"/>
+      <c r="I124" s="287"/>
+      <c r="J124" s="287"/>
+      <c r="K124" s="287"/>
+      <c r="L124" s="287"/>
+      <c r="M124" s="287"/>
+      <c r="N124" s="287"/>
     </row>
     <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="269"/>
-      <c r="C125" s="269"/>
-      <c r="D125" s="269"/>
-      <c r="E125" s="269"/>
-      <c r="F125" s="269"/>
-      <c r="G125" s="269"/>
-      <c r="H125" s="269"/>
-      <c r="I125" s="269"/>
-      <c r="J125" s="269"/>
-      <c r="K125" s="269"/>
-      <c r="L125" s="269"/>
-      <c r="M125" s="269"/>
-      <c r="N125" s="269"/>
+      <c r="B125" s="287"/>
+      <c r="C125" s="287"/>
+      <c r="D125" s="287"/>
+      <c r="E125" s="287"/>
+      <c r="F125" s="287"/>
+      <c r="G125" s="287"/>
+      <c r="H125" s="287"/>
+      <c r="I125" s="287"/>
+      <c r="J125" s="287"/>
+      <c r="K125" s="287"/>
+      <c r="L125" s="287"/>
+      <c r="M125" s="287"/>
+      <c r="N125" s="287"/>
     </row>
     <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="269"/>
-      <c r="C126" s="269"/>
-      <c r="D126" s="269"/>
-      <c r="E126" s="269"/>
-      <c r="F126" s="269"/>
-      <c r="G126" s="269"/>
-      <c r="H126" s="269"/>
-      <c r="I126" s="269"/>
-      <c r="J126" s="269"/>
-      <c r="K126" s="269"/>
-      <c r="L126" s="269"/>
-      <c r="M126" s="269"/>
-      <c r="N126" s="269"/>
+      <c r="B126" s="287"/>
+      <c r="C126" s="287"/>
+      <c r="D126" s="287"/>
+      <c r="E126" s="287"/>
+      <c r="F126" s="287"/>
+      <c r="G126" s="287"/>
+      <c r="H126" s="287"/>
+      <c r="I126" s="287"/>
+      <c r="J126" s="287"/>
+      <c r="K126" s="287"/>
+      <c r="L126" s="287"/>
+      <c r="M126" s="287"/>
+      <c r="N126" s="287"/>
     </row>
     <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="269"/>
-      <c r="C127" s="269"/>
-      <c r="D127" s="269"/>
-      <c r="E127" s="269"/>
-      <c r="F127" s="269"/>
-      <c r="G127" s="269"/>
-      <c r="H127" s="269"/>
-      <c r="I127" s="269"/>
-      <c r="J127" s="269"/>
-      <c r="K127" s="269"/>
-      <c r="L127" s="269"/>
-      <c r="M127" s="269"/>
-      <c r="N127" s="269"/>
+      <c r="B127" s="287"/>
+      <c r="C127" s="287"/>
+      <c r="D127" s="287"/>
+      <c r="E127" s="287"/>
+      <c r="F127" s="287"/>
+      <c r="G127" s="287"/>
+      <c r="H127" s="287"/>
+      <c r="I127" s="287"/>
+      <c r="J127" s="287"/>
+      <c r="K127" s="287"/>
+      <c r="L127" s="287"/>
+      <c r="M127" s="287"/>
+      <c r="N127" s="287"/>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B130">
@@ -10545,12 +10575,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10567,6 +10591,12 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10575,7 +10605,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:N41"/>
+  <dimension ref="C3:N42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -10614,9 +10644,9 @@
         <v>191</v>
       </c>
       <c r="J5" s="163"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
+      <c r="K5" s="321"/>
+      <c r="L5" s="321"/>
+      <c r="M5" s="321"/>
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="3:14" x14ac:dyDescent="0.3">
@@ -10633,12 +10663,12 @@
         <v>127</v>
       </c>
       <c r="H6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J6" s="163"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="K6" s="321"/>
+      <c r="L6" s="321"/>
+      <c r="M6" s="321"/>
       <c r="N6" s="19"/>
     </row>
     <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10646,39 +10676,39 @@
         <v>195</v>
       </c>
       <c r="J7" s="163"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
+      <c r="K7" s="321"/>
+      <c r="L7" s="321"/>
+      <c r="M7" s="321"/>
       <c r="N7" s="19"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="309" t="s">
-        <v>276</v>
-      </c>
-      <c r="D8" s="310"/>
-      <c r="E8" s="310"/>
-      <c r="F8" s="310"/>
-      <c r="G8" s="310"/>
-      <c r="H8" s="310"/>
-      <c r="I8" s="310"/>
-      <c r="J8" s="311"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="C8" s="313" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="314"/>
+      <c r="E8" s="314"/>
+      <c r="F8" s="314"/>
+      <c r="G8" s="314"/>
+      <c r="H8" s="314"/>
+      <c r="I8" s="314"/>
+      <c r="J8" s="315"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
       <c r="N8" s="19"/>
     </row>
     <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="312"/>
-      <c r="D9" s="313"/>
-      <c r="E9" s="313"/>
-      <c r="F9" s="313"/>
-      <c r="G9" s="313"/>
-      <c r="H9" s="313"/>
-      <c r="I9" s="313"/>
-      <c r="J9" s="314"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
+      <c r="C9" s="316"/>
+      <c r="D9" s="317"/>
+      <c r="E9" s="317"/>
+      <c r="F9" s="317"/>
+      <c r="G9" s="317"/>
+      <c r="H9" s="317"/>
+      <c r="I9" s="317"/>
+      <c r="J9" s="318"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="3:14" x14ac:dyDescent="0.3">
@@ -10703,6 +10733,8 @@
       <c r="H12" s="161"/>
       <c r="I12" s="161"/>
       <c r="J12" s="162"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
     </row>
     <row r="13" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C13" s="228" t="s">
@@ -10716,9 +10748,11 @@
         <v>191</v>
       </c>
       <c r="H13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J13" s="163"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
     </row>
     <row r="14" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C14" s="228" t="s">
@@ -10734,40 +10768,48 @@
         <v>127</v>
       </c>
       <c r="H14" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J14" s="163"/>
+      <c r="K14" s="321"/>
+      <c r="L14" s="321"/>
     </row>
     <row r="15" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="47" t="s">
         <v>195</v>
       </c>
       <c r="J15" s="163"/>
+      <c r="K15" s="321"/>
+      <c r="L15" s="321"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C16" s="309" t="s">
-        <v>279</v>
-      </c>
-      <c r="D16" s="310"/>
-      <c r="E16" s="310"/>
-      <c r="F16" s="310"/>
-      <c r="G16" s="310"/>
-      <c r="H16" s="310"/>
-      <c r="I16" s="310"/>
-      <c r="J16" s="311"/>
-    </row>
-    <row r="17" spans="3:10" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="312"/>
-      <c r="D17" s="313"/>
-      <c r="E17" s="313"/>
-      <c r="F17" s="313"/>
-      <c r="G17" s="313"/>
-      <c r="H17" s="313"/>
-      <c r="I17" s="313"/>
-      <c r="J17" s="314"/>
-    </row>
-    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="313" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="314"/>
+      <c r="E16" s="314"/>
+      <c r="F16" s="314"/>
+      <c r="G16" s="314"/>
+      <c r="H16" s="314"/>
+      <c r="I16" s="314"/>
+      <c r="J16" s="315"/>
+      <c r="K16" s="321"/>
+      <c r="L16" s="321"/>
+    </row>
+    <row r="17" spans="3:13" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="316"/>
+      <c r="D17" s="317"/>
+      <c r="E17" s="317"/>
+      <c r="F17" s="317"/>
+      <c r="G17" s="317"/>
+      <c r="H17" s="317"/>
+      <c r="I17" s="317"/>
+      <c r="J17" s="318"/>
+      <c r="K17" s="321"/>
+      <c r="L17" s="321"/>
+    </row>
+    <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C20" s="231" t="s">
         <v>188</v>
       </c>
@@ -10781,7 +10823,7 @@
       <c r="I20" s="161"/>
       <c r="J20" s="162"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C21" s="233" t="s">
         <v>189</v>
       </c>
@@ -10793,8 +10835,11 @@
         <v>191</v>
       </c>
       <c r="J21" s="163"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C22" s="233" t="s">
         <v>192</v>
       </c>
@@ -10808,40 +10853,49 @@
         <v>127</v>
       </c>
       <c r="H22" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J22" s="163"/>
-    </row>
-    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K22" s="321"/>
+      <c r="L22" s="321"/>
+      <c r="M22" s="321"/>
+    </row>
+    <row r="23" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="47" t="s">
         <v>195</v>
       </c>
       <c r="J23" s="163"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="309" t="s">
-        <v>283</v>
-      </c>
-      <c r="D24" s="310"/>
-      <c r="E24" s="310"/>
-      <c r="F24" s="310"/>
-      <c r="G24" s="310"/>
-      <c r="H24" s="310"/>
-      <c r="I24" s="310"/>
-      <c r="J24" s="311"/>
-    </row>
-    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="312"/>
-      <c r="D25" s="313"/>
-      <c r="E25" s="313"/>
-      <c r="F25" s="313"/>
-      <c r="G25" s="313"/>
-      <c r="H25" s="313"/>
-      <c r="I25" s="313"/>
-      <c r="J25" s="314"/>
-    </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="321"/>
+      <c r="L23" s="321"/>
+      <c r="M23" s="321"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C24" s="313" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="314"/>
+      <c r="E24" s="314"/>
+      <c r="F24" s="314"/>
+      <c r="G24" s="314"/>
+      <c r="H24" s="314"/>
+      <c r="I24" s="314"/>
+      <c r="J24" s="315"/>
+      <c r="K24" s="321"/>
+      <c r="L24" s="321"/>
+      <c r="M24" s="321"/>
+    </row>
+    <row r="25" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="316"/>
+      <c r="D25" s="317"/>
+      <c r="E25" s="317"/>
+      <c r="F25" s="317"/>
+      <c r="G25" s="317"/>
+      <c r="H25" s="317"/>
+      <c r="I25" s="317"/>
+      <c r="J25" s="318"/>
+    </row>
+    <row r="27" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C28" s="237" t="s">
         <v>188</v>
       </c>
@@ -10855,7 +10909,7 @@
       <c r="I28" s="161"/>
       <c r="J28" s="162"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C29" s="239" t="s">
         <v>189</v>
       </c>
@@ -10868,7 +10922,7 @@
       </c>
       <c r="J29" s="163"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C30" s="239" t="s">
         <v>192</v>
       </c>
@@ -10882,41 +10936,41 @@
         <v>127</v>
       </c>
       <c r="H30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J30" s="163"/>
     </row>
-    <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="239" t="s">
         <v>195</v>
       </c>
       <c r="D31" s="240"/>
       <c r="J31" s="163"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="309" t="s">
-        <v>281</v>
-      </c>
-      <c r="D32" s="310"/>
-      <c r="E32" s="310"/>
-      <c r="F32" s="310"/>
-      <c r="G32" s="310"/>
-      <c r="H32" s="310"/>
-      <c r="I32" s="310"/>
-      <c r="J32" s="311"/>
-    </row>
-    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="312"/>
-      <c r="D33" s="313"/>
-      <c r="E33" s="313"/>
-      <c r="F33" s="313"/>
-      <c r="G33" s="313"/>
-      <c r="H33" s="313"/>
-      <c r="I33" s="313"/>
-      <c r="J33" s="314"/>
-    </row>
-    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C32" s="313" t="s">
+        <v>279</v>
+      </c>
+      <c r="D32" s="314"/>
+      <c r="E32" s="314"/>
+      <c r="F32" s="314"/>
+      <c r="G32" s="314"/>
+      <c r="H32" s="314"/>
+      <c r="I32" s="314"/>
+      <c r="J32" s="315"/>
+    </row>
+    <row r="33" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="316"/>
+      <c r="D33" s="317"/>
+      <c r="E33" s="317"/>
+      <c r="F33" s="317"/>
+      <c r="G33" s="317"/>
+      <c r="H33" s="317"/>
+      <c r="I33" s="317"/>
+      <c r="J33" s="318"/>
+    </row>
+    <row r="35" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C36" s="245" t="s">
         <v>188</v>
       </c>
@@ -10929,8 +10983,10 @@
       <c r="H36" s="161"/>
       <c r="I36" s="161"/>
       <c r="J36" s="162"/>
-    </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="321"/>
+      <c r="L36" s="321"/>
+    </row>
+    <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="247" t="s">
         <v>189</v>
       </c>
@@ -10942,8 +10998,10 @@
         <v>191</v>
       </c>
       <c r="J37" s="163"/>
-    </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="321"/>
+      <c r="L37" s="321"/>
+    </row>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C38" s="247" t="s">
         <v>192</v>
       </c>
@@ -10957,38 +11015,50 @@
         <v>127</v>
       </c>
       <c r="H38" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J38" s="163"/>
-    </row>
-    <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K38" s="321"/>
+      <c r="L38" s="321"/>
+    </row>
+    <row r="39" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C39" s="247" t="s">
         <v>195</v>
       </c>
       <c r="D39" s="248"/>
       <c r="J39" s="163"/>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="309" t="s">
-        <v>285</v>
-      </c>
-      <c r="D40" s="310"/>
-      <c r="E40" s="310"/>
-      <c r="F40" s="310"/>
-      <c r="G40" s="310"/>
-      <c r="H40" s="310"/>
-      <c r="I40" s="310"/>
-      <c r="J40" s="311"/>
-    </row>
-    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="312"/>
-      <c r="D41" s="313"/>
-      <c r="E41" s="313"/>
-      <c r="F41" s="313"/>
-      <c r="G41" s="313"/>
-      <c r="H41" s="313"/>
-      <c r="I41" s="313"/>
-      <c r="J41" s="314"/>
+      <c r="K39" s="321"/>
+      <c r="L39" s="321"/>
+    </row>
+    <row r="40" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C40" s="313" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="314"/>
+      <c r="E40" s="314"/>
+      <c r="F40" s="314"/>
+      <c r="G40" s="314"/>
+      <c r="H40" s="314"/>
+      <c r="I40" s="314"/>
+      <c r="J40" s="315"/>
+      <c r="K40" s="321"/>
+      <c r="L40" s="321"/>
+    </row>
+    <row r="41" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="316"/>
+      <c r="D41" s="317"/>
+      <c r="E41" s="317"/>
+      <c r="F41" s="317"/>
+      <c r="G41" s="317"/>
+      <c r="H41" s="317"/>
+      <c r="I41" s="317"/>
+      <c r="J41" s="318"/>
+      <c r="K41" s="321"/>
+      <c r="L41" s="321"/>
+    </row>
+    <row r="42" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="K42" s="321"/>
+      <c r="L42" s="321"/>
     </row>
   </sheetData>
   <mergeCells count="5">
